--- a/CBT_2025_3회/산업안전기사_2025_3회_문항등록.xlsx
+++ b/CBT_2025_3회/산업안전기사_2025_3회_문항등록.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1471,17 +1471,17 @@
       </c>
       <c r="AG3" s="32" t="inlineStr">
         <is>
-          <t>연근로시간은 $1 {,} 000 \times 48 \times 52 \times 0.97 = 2 {,} 421 {,} 120$ 시간이다. $\text{도수율} = \dfrac{80}{2 {,} 421 {,} 120} \times 10^{6} \fallingdotseq 33.04$ 다.&lt;img src="safe_A_2025_03_001_exp1.png"&gt;&lt;em&gt;도수율과 강도율 — 곱하는 수가 다르다&lt;/em&gt;</t>
+          <t>연근로시간은 $1 {,} 000 \times 48 \times 52 \times 0.97 = 2 {,} 421 {,} 120$ 시간이다. $\text{도수율} = \dfrac{80}{2 {,} 421 {,} 120} \times 10^{6} \fallingdotseq 33.04$다.&lt;img src="safe_A_2025_03_001_exp1.png"&gt;&lt;em&gt;도수율과 강도율 — 곱하는 수가 다르다&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH3" s="32" t="inlineStr">
         <is>
-          <t>① 31.06 은 결근율을 잘못 잡았을 때 쪽이다.&lt;br&gt;② 32.05 도 계산과 맞지 않는다.&lt;br&gt;④ 34.03 은 결근을 빼지 않았을 때에 가깝다.</t>
+          <t>① 31.06은 결근율을 잘못 잡았을 때 쪽이다.&lt;br&gt;② 32.05 도 계산과 맞지 않는다.&lt;br&gt;④ 34.03은 결근을 빼지 않았을 때에 가깝다.</t>
         </is>
       </c>
       <c r="AI3" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;도수율(Frequency Rate)&lt;/strong&gt;&lt;br&gt;$\text{도수율} = \dfrac{\text{재해건수}}{\text{연근로시간}} \times 10^{6}$ 이다. &lt;strong&gt;결근율 3 [%] 를 빼야&lt;/strong&gt; 하므로 &lt;strong&gt;0.97 을 곱한다&lt;/strong&gt;. 이 보정을 빼먹으면 34.03 이 나와 함정에 걸린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;결근율을 빼고 100만을 곱한다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;도수율(Frequency Rate)&lt;/strong&gt;&lt;br&gt;$\text{도수율} = \dfrac{\text{재해건수}}{\text{연근로시간}} \times 10^{6}$이다. &lt;strong&gt;결근율 3 [%]를 빼야&lt;/strong&gt; 하므로 &lt;strong&gt;0.97을 곱한다&lt;/strong&gt;. 이 보정을 빼먹으면 34.03이 나와 함정에 걸린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;결근율을 빼고 100만을 곱한다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="AG5" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;터널 건설공사는 규모를 가리지 않고 모두&lt;/strong&gt; 제출 대상이다. 나머지 셋은 모두 기준에 못 미친다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;건설공사 유해위험방지계획서 제출 대상&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;공사&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기의 값&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;건축물 · 인공구조물&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;지상높이 &lt;u&gt;31 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;21 [m] 는 미달&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;다리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최대 지간길이 50 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;30 [m] 는 미달&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;터널&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;모든 터널 건설공사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;규모 조건이 없다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;굴착&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;깊이 &lt;u&gt;10 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5 [m] 는 미달&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;댐&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;저수용량 2천만 [t] 이상&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;터널 건설공사는 규모를 가리지 않고 모두&lt;/strong&gt; 제출 대상이다. 나머지 셋은 모두 기준에 못 미친다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;건설공사 유해위험방지계획서 제출 대상&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;공사&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기의 값&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;건축물 · 인공구조물&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;지상높이 &lt;u&gt;31 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;21 [m]는 미달&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;다리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최대 지간길이 50 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;30 [m]는 미달&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;터널&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;모든 터널 건설공사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;규모 조건이 없다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;굴착&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;깊이 &lt;u&gt;10 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5 [m]는 미달&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;댐&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;저수용량 2천만 [t] 이상&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH5" s="32" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="AG12" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;명령계통이 간단명료&lt;/strong&gt; 한 것이 라인형의 가장 큰 장점이다. 생산 계통을 그대로 타고 내려가기 때문이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전관리 조직의 세 갈래&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;형태&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;규모&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;장점&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단점&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;라인형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;100명 미만&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;명령계통이 간단명료&lt;/u&gt; · 지시가 빠르다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;안전 지식과 기술이 쌓이지 않는다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;스태프형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;100~1,000명&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;전문 지식과 기술이 쌓인다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;생산부서와 마찰&lt;/u&gt; · 명령계통과 조언이 혼동되기 쉽다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;라인·스태프형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;1,000명 이상&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;둘의 장점을 함께&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;권한 다툼과 조정에 시간&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;&lt;img src="safe_A_2025_03_010_exp1.png"&gt;&lt;em&gt;안전관리 조직 세 갈래 — 규모가 커질수록 참모가 붙는다&lt;/em&gt;</t>
+          <t>&lt;strong&gt;명령계통이 간단명료&lt;/strong&gt;한 것이 라인형의 가장 큰 장점이다. 생산 계통을 그대로 타고 내려가기 때문이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전관리 조직의 세 갈래&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;형태&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;규모&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;장점&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단점&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;라인형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;100명 미만&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;명령계통이 간단명료&lt;/u&gt; · 지시가 빠르다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;안전 지식과 기술이 쌓이지 않는다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;스태프형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;100~1,000명&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;전문 지식과 기술이 쌓인다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;생산부서와 마찰&lt;/u&gt; · 명령계통과 조언이 혼동되기 쉽다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;라인·스태프형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;1,000명 이상&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;둘의 장점을 함께&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;권한 다툼과 조정에 시간&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;&lt;img src="safe_A_2025_03_010_exp1.png"&gt;&lt;em&gt;안전관리 조직 세 갈래 — 규모가 커질수록 참모가 붙는다&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH12" s="32" t="inlineStr">
@@ -3003,17 +3003,17 @@
       </c>
       <c r="AG15" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;다수를 동시에 조직적으로 가르치는 것&lt;/strong&gt;은 Off.J.T 의 장점이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;O.J.T 와 Off.J.T&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;O.J.T&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;Off.J.T&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;어디서&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;일하는 자리에서&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;일터를 떠나 한자리에&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;누가 가르치나&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;직속 상사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;외부 전문가&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;인원&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개별 · 소수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;다수 동시&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;맞춤&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개인과 직장 실정에 맞춘다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;일률적&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;관계&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상호 신뢰와 이해가 깊어진다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;시설·교재&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;제한적&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전문 시설을 쓴다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;다수를 동시에 조직적으로 가르치는 것&lt;/strong&gt;은 Off.J.T의 장점이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;O.J.T와 Off.J.T&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;O.J.T&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;Off.J.T&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;어디서&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;일하는 자리에서&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;일터를 떠나 한자리에&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;누가 가르치나&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;직속 상사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;외부 전문가&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;인원&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개별 · 소수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;다수 동시&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;맞춤&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개인과 직장 실정에 맞춘다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;일률적&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;관계&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상호 신뢰와 이해가 깊어진다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;시설·교재&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;제한적&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전문 시설을 쓴다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH15" s="32" t="inlineStr">
         <is>
-          <t>② 개개인에게 맞춘 지도 훈련은 O.J.T 의 장점이다.&lt;br&gt;③ 상호 신뢰와 이해가 깊어지는 것도 O.J.T 다.&lt;br&gt;④ 직장 실정에 맞는 실제적 훈련도 O.J.T 다.</t>
+          <t>② 개개인에게 맞춘 지도 훈련은 O.J.T의 장점이다.&lt;br&gt;③ 상호 신뢰와 이해가 깊어지는 것도 O.J.T다.&lt;br&gt;④ 직장 실정에 맞는 실제적 훈련도 O.J.T다.</t>
         </is>
       </c>
       <c r="AI15" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;O.J.T(직장 내 교육)와 Off.J.T(직장 외 교육)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「다수」·「전문가」·「전문 시설」이 보이면 Off.J.T&lt;/strong&gt;다. 이 세 낱말만으로 대부분 갈린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;O.J.T 는 개별·계속, Off.J.T 는 다수·전문&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;O.J.T(직장 내 교육)와 Off.J.T(직장 외 교육)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「다수」·「전문가」·「전문 시설」이 보이면 Off.J.T&lt;/strong&gt;다. 이 세 낱말만으로 대부분 갈린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;O.J.T는 개별·계속, Off.J.T는 다수·전문&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3266,12 +3266,12 @@
       </c>
       <c r="AH17" s="32" t="inlineStr">
         <is>
-          <t>② MTP 는 중간 관리층을 대상으로 하는 40시간 과정이다.&lt;br&gt;③ ATT 는 훈련받은 사람이 다시 강사가 되는 방식이다.&lt;br&gt;④ CCS 는 최고경영층을 대상으로 한다.</t>
+          <t>② MTP는 중간 관리층을 대상으로 하는 40시간 과정이다.&lt;br&gt;③ ATT는 훈련받은 사람이 다시 강사가 되는 방식이다.&lt;br&gt;④ CCS는 최고경영층을 대상으로 한다.</t>
         </is>
       </c>
       <c r="AI17" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;기업 내 정형교육&lt;/strong&gt;&lt;br&gt;TWI 의 네 과정 — &lt;strong&gt;JIT(작업을 어떻게 가르치나) · JMT(작업을 어떻게 개선하나) · JRT(사람을 어떻게 다루나) · JST(안전을 어떻게 지키나)&lt;/strong&gt;. 문제에서 &lt;strong&gt;「지도하는 방법」과 「작업개선방법」&lt;/strong&gt;을 든 것이 곧 JIT 와 JMT 다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;제일선 감독자면 TWI&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;기업 내 정형교육&lt;/strong&gt;&lt;br&gt;TWI의 네 과정 — &lt;strong&gt;JIT(작업을 어떻게 가르치나) · JMT(작업을 어떻게 개선하나) · JRT(사람을 어떻게 다루나) · JST(안전을 어떻게 지키나)&lt;/strong&gt;. 문제에서 &lt;strong&gt;「지도하는 방법」과 「작업개선방법」&lt;/strong&gt;을 든 것이 곧 JIT와 JMT다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;제일선 감독자면 TWI&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="AG18" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;특별점검&lt;/strong&gt;이다. &lt;strong&gt;천재지변이나 이상사태가 났을 때&lt;/strong&gt; 하는 임시 점검이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전점검의 종류&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;종류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;언제&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;일상점검(수시점검)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업 전·중·후에 날마다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;작업자가 직접&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정기점검(계획점검)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;일정 기간마다 정기적으로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;월간 · 연간&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;특별점검&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;천재지변·이상사태 뒤 · 기계를 신설하거나 고친 뒤 · 오래 쓰지 않다가 다시 쓸 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;임시로&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;임시점검&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이상을 발견했을 때 곧바로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;특별점검&lt;/strong&gt;이다. &lt;strong&gt;천재지변이나 이상사태가 났을 때&lt;/strong&gt;하는 임시 점검이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전점검의 종류&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;종류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;언제&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;일상점검(수시점검)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업 전·중·후에 날마다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;작업자가 직접&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정기점검(계획점검)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;일정 기간마다 정기적으로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;월간 · 연간&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;특별점검&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;천재지변·이상사태 뒤 · 기계를 신설하거나 고친 뒤 · 오래 쓰지 않다가 다시 쓸 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;임시로&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;임시점검&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이상을 발견했을 때 곧바로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH18" s="32" t="inlineStr">
@@ -3519,17 +3519,17 @@
       </c>
       <c r="AG19" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;연천인율 = 도수율 × 2.4&lt;/strong&gt;이므로 $\text{도수율} = 45 / 2.4 = 18.75$ 다.</t>
+          <t>&lt;strong&gt;연천인율 = 도수율 × 2.4&lt;/strong&gt;이므로 $\text{도수율} = 45 / 2.4 = 18.75$다.</t>
         </is>
       </c>
       <c r="AH19" s="32" t="inlineStr">
         <is>
-          <t>① 10.8 은 계산과 맞지 않는다.&lt;br&gt;③ 108 은 자릿수가 어긋난다.&lt;br&gt;④ 187.5 도 어긋난다.</t>
+          <t>① 10.8은 계산과 맞지 않는다.&lt;br&gt;③ 108은 자릿수가 어긋난다.&lt;br&gt;④ 187.5 도 어긋난다.</t>
         </is>
       </c>
       <c r="AI19" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;연천인율과 도수율의 관계&lt;/strong&gt;&lt;br&gt;한 사람이 &lt;strong&gt;연간 2,400시간&lt;/strong&gt; 일한다고 보면, $\text{연천인율} = \dfrac{\text{재해자수}}{\text{근로자수}} \times 1 {,} 000$ 과 $\text{도수율} = \dfrac{\text{재해건수}}{\text{연근로시간}} \times 10^{6}$ 사이에 &lt;strong&gt;2.4배&lt;/strong&gt;의 관계가 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;연천인율 = 도수율 × 2.4&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;연천인율과 도수율의 관계&lt;/strong&gt;&lt;br&gt;한 사람이 &lt;strong&gt;연간 2,400시간&lt;/strong&gt; 일한다고 보면, $\text{연천인율} = \dfrac{\text{재해자수}}{\text{근로자수}} \times 1 {,} 000$과 $\text{도수율} = \dfrac{\text{재해건수}}{\text{연근로시간}} \times 10^{6}$ 사이에 &lt;strong&gt;2.4배&lt;/strong&gt;의 관계가 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;연천인율 = 도수율 × 2.4&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4043,17 +4043,17 @@
       </c>
       <c r="AG23" s="32" t="inlineStr">
         <is>
-          <t>$T = A \cdot B = ( X_{1} + X_{2} ) ( X_{1} + X_{3} )$ 다. 전개하면 $X_{1} + X_{1} X_{3} + X_{1} X_{2} + X_{2} X_{3}$ 이고, $X_{1}$&lt;strong&gt; 이 &lt;/strong&gt;$X_{1} X_{2}$&lt;strong&gt; 와 &lt;/strong&gt;$X_{1} X_{3}$&lt;strong&gt; 를 흡수&lt;/strong&gt; 하므로 $T = X_{1} + X_{2} X_{3}$ 다. 보기 가운데 최소 컷셋을 담은 것은 &lt;strong&gt;[X₁]&lt;/strong&gt; 뿐이다.&lt;img src="safe_A_2025_03_021_exp1.png"&gt;&lt;em&gt;AND 아래 OR 둘 — 겹치는 사상이 나머지를 흡수한다&lt;/em&gt;</t>
+          <t>$T = A \cdot B = ( X_{1} + X_{2} ) ( X_{1} + X_{3} )$다. 전개하면 $X_{1} + X_{1} X_{3} + X_{1} X_{2} + X_{2} X_{3}$이고, $X_{1}$&lt;strong&gt;이 &lt;/strong&gt;$X_{1} X_{2}$&lt;strong&gt;와 &lt;/strong&gt;$X_{1} X_{3}$&lt;strong&gt;를 흡수&lt;/strong&gt;하므로 $T = X_{1} + X_{2} X_{3}$다. 보기 가운데 최소 컷셋을 담은 것은 &lt;strong&gt;[X₁]&lt;/strong&gt;뿐이다.&lt;img src="safe_A_2025_03_021_exp1.png"&gt;&lt;em&gt;AND 아래 OR 둘 — 겹치는 사상이 나머지를 흡수한다&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH23" s="32" t="inlineStr">
         <is>
-          <t>② [X₂] 만으로는 정상사상이 일어나지 않는다.&lt;br&gt;③ [X₁, X₂, X₃] 는 최소가 아니다.&lt;br&gt;④ [X₁, X₂] 와 [X₁, X₃] 는 컷셋이지만 $X_{1}$ 에 흡수되어 최소가 아니다.</t>
+          <t>② [X₂] 만으로는 정상사상이 일어나지 않는다.&lt;br&gt;③ [X₁, X₂, X₃]는 최소가 아니다.&lt;br&gt;④ [X₁, X₂]와 [X₁, X₃]는 컷셋이지만 $X_{1}$에 흡수되어 최소가 아니다.</t>
         </is>
       </c>
       <c r="AI23" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;최소 컷셋(Minimal Cut Set)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;부울대수의 흡수법칙 &lt;/strong&gt;$A + AB = A$를 쓴다. 컷셋 가운데 &lt;strong&gt;다른 컷셋을 통째로 품고 있는 것&lt;/strong&gt;은 최소가 아니다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;작은 것이 큰 것을 흡수한다&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 엄밀히 따지면 이 FT 도의 최소 컷셋은 &lt;u&gt;[X₁] 과 [X₂, X₃] 둘&lt;/u&gt;이다. 보기에 그 둘을 함께 담은 항목이 없어 &lt;u&gt;[X₁] 만 든 ①이 정답&lt;/u&gt;으로 처리되었다. 계산은 $T = X_{1} + X_{2} X_{3}$까지 해 두고 보기를 고르는 것이 옳다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;최소 컷셋(Minimal Cut Set)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;부울대수의 흡수법칙 &lt;/strong&gt;$A + AB = A$를 쓴다. 컷셋 가운데 &lt;strong&gt;다른 컷셋을 통째로 품고 있는 것&lt;/strong&gt;은 최소가 아니다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;작은 것이 큰 것을 흡수한다&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 엄밀히 따지면 이 FT 도의 최소 컷셋은 &lt;u&gt;[X₁]과 [X₂, X₃] 둘&lt;/u&gt;이다. 보기에 그 둘을 함께 담은 항목이 없어 &lt;u&gt;[X₁] 만 든 ①이 정답&lt;/u&gt;으로 처리되었다. 계산은 $T = X_{1} + X_{2} X_{3}$까지 해 두고 보기를 고르는 것이 옳다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="AH24" s="32" t="inlineStr">
         <is>
-          <t>② commission error 는 했지만 잘못한 오류다.&lt;br&gt;③ sequence error 는 순서를 뒤바꾼 오류다.&lt;br&gt;④ timing error 는 너무 빠르거나 늦은 오류다.</t>
+          <t>② commission error는 했지만 잘못한 오류다.&lt;br&gt;③ sequence error는 순서를 뒤바꾼 오류다.&lt;br&gt;④ timing error는 너무 빠르거나 늦은 오류다.</t>
         </is>
       </c>
       <c r="AI24" s="32" t="inlineStr">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="AG25" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;S 는 Standard 가 아니라 Simplify&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;작업개선의 원리 ECRS&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;글자&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 묻나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;E — Eliminate&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;없앤다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 일이 꼭 필요한가&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;C — Combine&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;합친다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;다른 일과 묶을 수 없나&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;R — Rearrange&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;순서를 바꾼다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;순서를 바꾸면 나아지나&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;S — Simplify&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;단순하게 만든다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;더 쉽게 할 수 없나&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;S는 Standard가 아니라 Simplify&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;작업개선의 원리 ECRS&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;글자&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 묻나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;E — Eliminate&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;없앤다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 일이 꼭 필요한가&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;C — Combine&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;합친다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;다른 일과 묶을 수 없나&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;R — Rearrange&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;순서를 바꾼다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;순서를 바꾸면 나아지나&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;S — Simplify&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;단순하게 만든다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;더 쉽게 할 수 없나&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH25" s="32" t="inlineStr">
         <is>
-          <t>① Combine(합치기)은 ECRS 의 하나다.&lt;br&gt;③ Eliminate(없애기)도 그렇다.&lt;br&gt;④ Rearrange(재배열)도 그렇다.</t>
+          <t>① Combine(합치기)은 ECRS의 하나다.&lt;br&gt;③ Eliminate(없애기)도 그렇다.&lt;br&gt;④ Rearrange(재배열)도 그렇다.</t>
         </is>
       </c>
       <c r="AI25" s="32" t="inlineStr">
@@ -4793,12 +4793,12 @@
       </c>
       <c r="AG29" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;럭스(lux)&lt;/strong&gt;는 &lt;strong&gt;조도&lt;/strong&gt;의 단위다. 소리와 무관하다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;음량 관련 척도와 조명 관련 단위&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단위&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 재나&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;phon&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;감각적 크기 수준&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;1,000 [Hz] 순음의 dB 값&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;sone&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;느끼는 크기의 비율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;40 [phon] 이 1 [sone]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;PNdB / PLdB&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;인식소음 수준&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;항공기 소음 평가&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;lux&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;조도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;단위면적당 도달하는 광속&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;lumen&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;광속&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;광원이 내는 빛의 양&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;cd/m²&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;휘도&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;보이는 밝기&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;럭스(lux)&lt;/strong&gt;는 &lt;strong&gt;조도&lt;/strong&gt;의 단위다. 소리와 무관하다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;음량 관련 척도와 조명 관련 단위&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단위&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 재나&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;phon&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;감각적 크기 수준&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;1,000 [Hz] 순음의 dB 값&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;sone&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;느끼는 크기의 비율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;40 [phon]이 1 [sone]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;PNdB / PLdB&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;인식소음 수준&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;항공기 소음 평가&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;lux&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;조도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;단위면적당 도달하는 광속&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;lumen&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;광속&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;광원이 내는 빛의 양&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;cd/m²&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;휘도&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;보이는 밝기&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH29" s="32" t="inlineStr">
         <is>
-          <t>① sone 은 음량 척도다.&lt;br&gt;③ phon 도 음량 척도다.&lt;br&gt;④ 인식소음 수준(PNdB)도 음량 척도다.</t>
+          <t>① sone은 음량 척도다.&lt;br&gt;③ phon 도 음량 척도다.&lt;br&gt;④ 인식소음 수준(PNdB)도 음량 척도다.</t>
         </is>
       </c>
       <c r="AI29" s="32" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="U30" s="32" t="inlineStr">
         <is>
-          <t>FMEA 의 장점이라 할 수 있는 것은?</t>
+          <t>FMEA의 장점이라 할 수 있는 것은?</t>
         </is>
       </c>
       <c r="V30" s="32" t="inlineStr"/>
@@ -4922,17 +4922,17 @@
       </c>
       <c r="AG30" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;서식이 간단하고 적은 노력으로 할 수 있다&lt;/strong&gt;는 것이 FMEA 의 가장 큰 장점이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FMEA 의 장단점&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;장점&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단점&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td rowspan="3" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;내용&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;서식이 간단하고 적은 노력으로 분석&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;논리적 배경이 약하다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td rowspan="2" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;부품 하나하나의 고장 영향을 빠짐없이 본다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;두 가지 이상이 겹쳐 고장 나는 경우에 약하다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;인적 요소는 분석 대상이 아니다&lt;/u&gt; — 물적 요소만&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;서식이 간단하고 적은 노력으로 할 수 있다&lt;/strong&gt;는 것이 FMEA의 가장 큰 장점이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FMEA의 장단점&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;장점&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단점&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td rowspan="3" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;내용&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;서식이 간단하고 적은 노력으로 분석&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;논리적 배경이 약하다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td rowspan="2" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;부품 하나하나의 고장 영향을 빠짐없이 본다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;두 가지 이상이 겹쳐 고장 나는 경우에 약하다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;인적 요소는 분석 대상이 아니다&lt;/u&gt; — 물적 요소만&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH30" s="32" t="inlineStr">
         <is>
-          <t>① 논리적 배경이 강한 것은 FTA 쪽이다.&lt;br&gt;② FMEA 는 물적 요소만 다루며 인적 요소는 대상이 아니다.&lt;br&gt;④ 두 가지 이상이 겹쳐 고장 나는 경우에는 오히려 약하다.</t>
+          <t>① 논리적 배경이 강한 것은 FTA 쪽이다.&lt;br&gt;② FMEA는 물적 요소만 다루며 인적 요소는 대상이 아니다.&lt;br&gt;④ 두 가지 이상이 겹쳐 고장 나는 경우에는 오히려 약하다.</t>
         </is>
       </c>
       <c r="AI30" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FMEA 의 장단점&lt;/strong&gt;&lt;br&gt;보기 ①②④가 모두 &lt;strong&gt;FMEA 의 단점을 장점인 척 뒤집어 놓은&lt;/strong&gt; 것이다. &lt;strong&gt;논리적 배경 · 인적 요소 · 중복 고장&lt;/strong&gt; 셋은 모두 FMEA 가 못하는 일이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;간단한 것이 장점, 논리가 약한 것이 단점&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FMEA의 장단점&lt;/strong&gt;&lt;br&gt;보기 ①②④가 모두 &lt;strong&gt;FMEA의 단점을 장점인 척 뒤집어 놓은&lt;/strong&gt; 것이다. &lt;strong&gt;논리적 배경 · 인적 요소 · 중복 고장&lt;/strong&gt; 셋은 모두 FMEA가 못하는 일이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;간단한 것이 장점, 논리가 약한 것이 단점&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5051,12 +5051,12 @@
       </c>
       <c r="AG31" s="32" t="inlineStr">
         <is>
-          <t>$\beta$ 는 &lt;strong&gt;판별기준점에서 신호분포의 높이와 잡음분포의 높이의 비&lt;/strong&gt;다. &lt;strong&gt;두 곡선이 만나는 자리&lt;/strong&gt; 에서는 두 높이가 같으므로 $\beta = 1$ 이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;판별기준 $\beta$ 의 뜻&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;$\beta$&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준의 위치&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;어떤 태도인가&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;$\beta = 1$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;두 곡선이 만나는 자리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;중립&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;$\beta &amp;lt; 1$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;왼쪽으로 옮김&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;적극적&lt;/u&gt; — 누락은 줄고 &lt;u&gt;허위경보가 는다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;$\beta &amp;gt; 1$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;오른쪽으로 옮김&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;보수적&lt;/u&gt; — 허위경보는 줄고 &lt;u&gt;누락이 는다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$\beta$는 &lt;strong&gt;판별기준점에서 신호분포의 높이와 잡음분포의 높이의 비&lt;/strong&gt;다. &lt;strong&gt;두 곡선이 만나는 자리&lt;/strong&gt; 에서는 두 높이가 같으므로 $\beta = 1$이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;판별기준 $\beta$의 뜻&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;$\beta$&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준의 위치&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;어떤 태도인가&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;$\beta = 1$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;두 곡선이 만나는 자리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;중립&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;$\beta &amp;lt; 1$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;왼쪽으로 옮김&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;적극적&lt;/u&gt; — 누락은 줄고 &lt;u&gt;허위경보가 는다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;$\beta &amp;gt; 1$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;오른쪽으로 옮김&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;보수적&lt;/u&gt; — 허위경보는 줄고 &lt;u&gt;누락이 는다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH31" s="32" t="inlineStr">
         <is>
-          <t>① $\beta = 0$ 은 나올 수 없는 값이다.&lt;br&gt;② $\beta &amp;lt; 1$ 은 기준을 왼쪽으로 옮겼을 때다.&lt;br&gt;④ $\beta &amp;gt; 1$ 은 기준을 오른쪽으로 옮겼을 때다.</t>
+          <t>① $\beta = 0$은 나올 수 없는 값이다.&lt;br&gt;② $\beta &amp;lt; 1$은 기준을 왼쪽으로 옮겼을 때다.&lt;br&gt;④ $\beta &amp;gt; 1$은 기준을 오른쪽으로 옮겼을 때다.</t>
         </is>
       </c>
       <c r="AI31" s="32" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="AI32" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;공분산과 독립성&lt;/strong&gt;&lt;br&gt;FTA 의 확률 계산(&lt;strong&gt;AND 는 곱, OR 는 &lt;/strong&gt;$1 - \prod ( 1 - q )$)은 &lt;strong&gt;기본사상들이 서로 독립&lt;/strong&gt;이라는 전제 위에서 성립한다. 독립이 아니면 그 식이 맞지 않으므로 먼저 확인해야 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;독립이면 공분산이 0&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;공분산과 독립성&lt;/strong&gt;&lt;br&gt;FTA의 확률 계산(&lt;strong&gt;AND는 곱, OR는 &lt;/strong&gt;$1 - \prod ( 1 - q )$)은 &lt;strong&gt;기본사상들이 서로 독립&lt;/strong&gt;이라는 전제 위에서 성립한다. 독립이 아니면 그 식이 맞지 않으므로 먼저 확인해야 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;독립이면 공분산이 0&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5309,12 +5309,12 @@
       </c>
       <c r="AG33" s="32" t="inlineStr">
         <is>
-          <t>병렬은 $R = 1 - ( 1 - 0.40 ) ( 1 - 0.95 ) = 1 - 0.60 \times 0.05 = 1 - 0.03 = 0.97$ 이다.&lt;img src="safe_A_2025_03_031_exp1.png"&gt;&lt;em&gt;직렬과 병렬 — 하나만 고장 나도 멈추면 직렬이다&lt;/em&gt;</t>
+          <t>병렬은 $R = 1 - ( 1 - 0.40 ) ( 1 - 0.95 ) = 1 - 0.60 \times 0.05 = 1 - 0.03 = 0.97$이다.&lt;img src="safe_A_2025_03_031_exp1.png"&gt;&lt;em&gt;직렬과 병렬 — 하나만 고장 나도 멈추면 직렬이다&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH33" s="32" t="inlineStr">
         <is>
-          <t>① 0.89 는 계산과 맞지 않는다.&lt;br&gt;② 0.92 도 맞지 않는다.&lt;br&gt;③ 0.95 는 기계 하나의 신뢰도다.</t>
+          <t>① 0.89는 계산과 맞지 않는다.&lt;br&gt;② 0.92 도 맞지 않는다.&lt;br&gt;③ 0.95는 기계 하나의 신뢰도다.</t>
         </is>
       </c>
       <c r="AI33" s="32" t="inlineStr">
@@ -5572,12 +5572,12 @@
       </c>
       <c r="AH35" s="32" t="inlineStr">
         <is>
-          <t>① 0~1 RMR 은 경작업의 아래쪽이다.&lt;br&gt;③ 4~7 RMR 은 중(重)작업이다.&lt;br&gt;④ 7~9 RMR 은 초중작업 영역이다.</t>
+          <t>① 0~1 RMR은 경작업의 아래쪽이다.&lt;br&gt;③ 4~7 RMR은 중(重)작업이다.&lt;br&gt;④ 7~9 RMR은 초중작업 영역이다.</t>
         </is>
       </c>
       <c r="AI35" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;에너지대사율(RMR)&lt;/strong&gt;&lt;br&gt;$\mathrm{RMR} = \dfrac{\text{작업 시 소비에너지} - \text{안정 시 소비에너지}}{\text{기초대사량}}$ 이다. &lt;strong&gt;0 · 2 · 4 · 7&lt;/strong&gt;이 경계값이며, &lt;strong&gt;한자 中과 重이 다르다&lt;/strong&gt;는 점에 주의한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;0-2-4-7&lt;/u&gt; — 보통작업은 2~4.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;에너지대사율(RMR)&lt;/strong&gt;&lt;br&gt;$\mathrm{RMR} = \dfrac{\text{작업 시 소비에너지} - \text{안정 시 소비에너지}}{\text{기초대사량}}$이다. &lt;strong&gt;0 · 2 · 4 · 7&lt;/strong&gt;이 경계값이며, &lt;strong&gt;한자 中과 重이 다르다&lt;/strong&gt;는 점에 주의한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;0-2-4-7&lt;/u&gt; — 보통작업은 2~4.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="AG37" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;정해진 절차를 빠르고 정확하게 되풀이&lt;/strong&gt; 하는 것은 기계가 압도적으로 낫다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;인간과 기계, 어느 쪽이 나은가&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기능&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;인간&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기계&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;귀납적 추리 · 일반화&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;○&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;원칙을 적용해 문제 해결&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;○&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;경험을 바탕으로 한 의사결정&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;○&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;예기치 못한 사건의 감지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;○&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;명시된 절차의 신속·정량적 처리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;○&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연역적 추리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;○&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;반복 작업의 신뢰성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;○&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대량 정보의 보관&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;○&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;정해진 절차를 빠르고 정확하게 되풀이&lt;/strong&gt;하는 것은 기계가 압도적으로 낫다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;인간과 기계, 어느 쪽이 나은가&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기능&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;인간&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기계&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;귀납적 추리 · 일반화&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;○&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;원칙을 적용해 문제 해결&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;○&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;경험을 바탕으로 한 의사결정&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;○&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;예기치 못한 사건의 감지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;○&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;명시된 절차의 신속·정량적 처리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;○&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연역적 추리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;○&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;반복 작업의 신뢰성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;○&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대량 정보의 보관&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;○&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH37" s="32" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="AI37" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;인간-기계 시스템의 기능 배분&lt;/strong&gt;&lt;br&gt;가르는 물음 — &lt;strong&gt;처음 겪는 일을 다뤄야 하는가&lt;/strong&gt;. 예상 밖의 상황을 판단하는 것은 사람, &lt;strong&gt;정해진 것을 빠르고 정확히 되풀이&lt;/strong&gt; 하는 것은 기계다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;사람은 귀납, 기계는 연역&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;인간-기계 시스템의 기능 배분&lt;/strong&gt;&lt;br&gt;가르는 물음 — &lt;strong&gt;처음 겪는 일을 다뤄야 하는가&lt;/strong&gt;. 예상 밖의 상황을 판단하는 것은 사람, &lt;strong&gt;정해진 것을 빠르고 정확히 되풀이&lt;/strong&gt;하는 것은 기계다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;사람은 귀납, 기계는 연역&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="AG38" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;「작업환경 평가」&lt;/strong&gt;라는 단계는 없다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전성 평가 6단계&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 하나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;관계 자료의 정비검토&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;설계도 · 공정도 · 물질 자료&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정성적 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;입지 조건 · 배치 · 건조물 · 소방설비 · 원재료 · 공정&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정량적 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;취급물질 · 용량 · 온도 · 압력 · 조작&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전대책&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;설비 대책과 관리 대책&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;재해정보에 의한 재평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;비슷한 사고 사례로&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;FTA 에 의한 재평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;등급 Ⅰ·Ⅱ 에 적용&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;「작업환경 평가」&lt;/strong&gt;라는 단계는 없다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전성 평가 6단계&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 하나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;관계 자료의 정비검토&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;설계도 · 공정도 · 물질 자료&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정성적 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;입지 조건 · 배치 · 건조물 · 소방설비 · 원재료 · 공정&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정량적 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;취급물질 · 용량 · 온도 · 압력 · 조작&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전대책&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;설비 대책과 관리 대책&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;재해정보에 의한 재평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;비슷한 사고 사례로&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;FTA에 의한 재평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;등급 Ⅰ·Ⅱ 에 적용&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH38" s="32" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="AG39" s="32" t="inlineStr">
         <is>
-          <t>FTA 는 &lt;strong&gt;정성적 해석도 정량적 해석도 모두&lt;/strong&gt; 할 수 있다. 「정성적 해석이 불가능하다」는 틀렸다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA 의 특징&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;특징&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Top Down 형식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;정상사상에서 아래로 캐 내려간다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연역적 해석&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;결과에서 원인으로&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;특정 사상에 대한 해석&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;정상사상 하나를 정해 놓고 본다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;논리기호를 사용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;AND · OR 게이트&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정성적 · 정량적 해석이 모두 가능&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「불가능」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;컴퓨터 처리가 가능&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>FTA는 &lt;strong&gt;정성적 해석도 정량적 해석도 모두&lt;/strong&gt;할 수 있다. 「정성적 해석이 불가능하다」는 틀렸다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA의 특징&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;특징&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Top Down 형식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;정상사상에서 아래로 캐 내려간다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연역적 해석&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;결과에서 원인으로&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;특정 사상에 대한 해석&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;정상사상 하나를 정해 놓고 본다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;논리기호를 사용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;AND · OR 게이트&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정성적 · 정량적 해석이 모두 가능&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「불가능」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;컴퓨터 처리가 가능&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH39" s="32" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="AI39" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FTA 의 특징&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;FTA 는 정량적 해석까지 되는 것이 강점&lt;/strong&gt;이다. FMEA 가 정성적에 머무는 것과 대비된다. 「불가능」이라는 말이 붙으면 대개 오답이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;FTA 는 정성도 정량도 된다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FTA의 특징&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;FTA는 정량적 해석까지 되는 것이 강점&lt;/strong&gt;이다. FMEA가 정성적에 머무는 것과 대비된다. 「불가능」이라는 말이 붙으면 대개 오답이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;FTA는 정성도 정량도 된다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6603,12 +6603,12 @@
       </c>
       <c r="AG43" s="32" t="inlineStr">
         <is>
-          <t>평형플랜지의 지름은 &lt;strong&gt;숫돌 지름의 1/3 이상&lt;/strong&gt; 이어야 한다. $180 / 3 = 60$ [mm] 다.&lt;img src="safe_A_2025_03_041_exp1.png"&gt;&lt;em&gt;연삭기의 숫자 묶음&lt;/em&gt;</t>
+          <t>평형플랜지의 지름은 &lt;strong&gt;숫돌 지름의 1/3 이상&lt;/strong&gt; 이어야 한다. $180 / 3 = 60$ [mm]다.&lt;img src="safe_A_2025_03_041_exp1.png"&gt;&lt;em&gt;연삭기의 숫자 묶음&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH43" s="32" t="inlineStr">
         <is>
-          <t>① 30 [mm] 는 1/6 이라 기준에 못 미친다.&lt;br&gt;② 40 [mm] 도 못 미친다.&lt;br&gt;③ 50 [mm] 도 못 미친다.</t>
+          <t>① 30 [mm]는 1/6이라 기준에 못 미친다.&lt;br&gt;② 40 [mm] 도 못 미친다.&lt;br&gt;③ 50 [mm] 도 못 미친다.</t>
         </is>
       </c>
       <c r="AI43" s="32" t="inlineStr">
@@ -6861,17 +6861,17 @@
       </c>
       <c r="AG45" s="32" t="inlineStr">
         <is>
-          <t>$V = \pi D N = \pi \times 0.2 \times 300 \fallingdotseq 188.5$ [m/min] 이다.</t>
+          <t>$V = \pi D N = \pi \times 0.2 \times 300 \fallingdotseq 188.5$ [m/min]이다.</t>
         </is>
       </c>
       <c r="AH45" s="32" t="inlineStr">
         <is>
-          <t>① 60.0 은 $\pi$ 를 곱하지 않았을 때 쪽이다.&lt;br&gt;② 94.2 는 반지름을 썼을 때 나온다.&lt;br&gt;③ 150.0 도 계산과 맞지 않는다.</t>
+          <t>① 60.0은 $\pi$를 곱하지 않았을 때 쪽이다.&lt;br&gt;② 94.2는 반지름을 썼을 때 나온다.&lt;br&gt;③ 150.0 도 계산과 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI45" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;원주속도 $V = \pi D N$&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;[m/min] 이면 D 를 [m] 로&lt;/strong&gt;, &lt;strong&gt;[m/s] 면 &lt;/strong&gt;$\pi D N / 60$이다. &lt;strong&gt;반지름이 아니라 지름&lt;/strong&gt;을 쓴다는 것도 실수하기 쉬운 자리다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;지름을 미터로 바꿔 &lt;/u&gt;$\pi$&lt;u&gt; 와 회전수를 곱한다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;원주속도 $V = \pi D N$&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;[m/min] 이면 D를 [m]로&lt;/strong&gt;, &lt;strong&gt;[m/s] 면 &lt;/strong&gt;$\pi D N / 60$이다. &lt;strong&gt;반지름이 아니라 지름&lt;/strong&gt;을 쓴다는 것도 실수하기 쉬운 자리다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;지름을 미터로 바꿔 &lt;/u&gt;$\pi$&lt;u&gt;와 회전수를 곱한다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7511,12 +7511,12 @@
       </c>
       <c r="AH50" s="32" t="inlineStr">
         <is>
-          <t>② 240 은 [mm] 값이지 [cm] 가 아니다.&lt;br&gt;③ 15 [cm] 는 계산과 맞지 않는다.&lt;br&gt;④ 150 [cm] 도 맞지 않는다.</t>
+          <t>② 240은 [mm] 값이지 [cm]가 아니다.&lt;br&gt;③ 15 [cm]는 계산과 맞지 않는다.&lt;br&gt;④ 150 [cm] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI50" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;양수기동식 방호장치의 안전거리&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;답은 [mm] 로 나오므로 물음의 단위를 확인&lt;/strong&gt; 해야 한다. 이 문항은 [cm] 를 물었으므로 10으로 나눈다. &lt;strong&gt;240 [mm] 와 24 [cm] 를 나란히 보기에 둔&lt;/strong&gt; 것이 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1,600 × 시간 = [mm]&lt;/u&gt; — 단위를 맞춘다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;양수기동식 방호장치의 안전거리&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;답은 [mm]로 나오므로 물음의 단위를 확인&lt;/strong&gt;해야 한다. 이 문항은 [cm]를 물었으므로 10으로 나눈다. &lt;strong&gt;240 [mm]와 24 [cm]를 나란히 보기에 둔&lt;/strong&gt; 것이 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1,600 × 시간 = [mm]&lt;/u&gt; — 단위를 맞춘다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7609,11 @@
           <t>&amp;lt; 와이어로프 지름 및 절단강도 &amp;gt;&lt;br&gt;10 [mm] — 56 [kN]      12 [mm] — 88 [kN]&lt;br&gt;14 [mm] — 110 [kN]     16 [mm] — 144 [kN]</t>
         </is>
       </c>
-      <c r="W51" s="32" t="inlineStr"/>
+      <c r="W51" s="32" t="inlineStr">
+        <is>
+          <t>safe_A_2025_03_049_stem1.png</t>
+        </is>
+      </c>
       <c r="X51" s="32" t="inlineStr">
         <is>
           <t>10mm</t>
@@ -7639,17 +7643,17 @@
       </c>
       <c r="AG51" s="32" t="inlineStr">
         <is>
-          <t>전체 하중은 $3 {,} 000 \times 9.8 = 29.4$ [kN] 이고, 로프 하나의 장력은 $T = \dfrac{29.4}{2 \cos 45 ^{\circ}} \fallingdotseq 20.79$ [kN] 이다. &lt;strong&gt;안전계수 5&lt;/strong&gt;를 곱하면 필요 절단강도가 $104$ [kN] 이므로, 이를 넘는 가장 작은 &lt;strong&gt;110 [kN] · 14 [mm]&lt;/strong&gt;를 고른다.&lt;img src="safe_A_2025_03_049_exp1.png"&gt;&lt;em&gt;줄걸이 각도와 장력 — 벌어질수록 로프에 걸리는 힘이 커진다&lt;/em&gt;</t>
+          <t>전체 하중은 $3 {,} 000 \times 9.8 = 29.4$ [kN]이고, 로프 하나의 장력은 $T = \dfrac{29.4}{2 \cos 45 ^{\circ}} \fallingdotseq 20.79$ [kN]이다. &lt;strong&gt;안전계수 5&lt;/strong&gt;를 곱하면 필요 절단강도가 $104$ [kN]이므로, 이를 넘는 가장 작은 &lt;strong&gt;110 [kN] · 14 [mm]&lt;/strong&gt;를 고른다.&lt;img src="safe_A_2025_03_049_exp1.png"&gt;&lt;em&gt;줄걸이 각도와 장력 — 벌어질수록 로프에 걸리는 힘이 커진다&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH51" s="32" t="inlineStr">
         <is>
-          <t>① 10 [mm](56 [kN])는 필요 강도에 크게 못 미친다.&lt;br&gt;② 12 [mm](88 [kN])도 104 [kN] 에 못 미친다.&lt;br&gt;④ 16 [mm](144 [kN])는 조건을 넘지만 「가장 작은 것」이 아니다.</t>
+          <t>① 10 [mm](56 [kN])는 필요 강도에 크게 못 미친다.&lt;br&gt;② 12 [mm](88 [kN])도 104 [kN]에 못 미친다.&lt;br&gt;④ 16 [mm](144 [kN])는 조건을 넘지만 「가장 작은 것」이 아니다.</t>
         </is>
       </c>
       <c r="AI51" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;줄걸이 각도와 와이어로프의 안전계수&lt;/strong&gt;&lt;br&gt;$T = \dfrac{W}{2 \cos \theta}$ 다. &lt;strong&gt;각도가 벌어질수록 장력이 커진다&lt;/strong&gt; — 60° 면 $W$ 그대로, 75° 면 약 1.93배가 된다. 양중기 달기구의 안전계수는 &lt;strong&gt;달기 와이어로프·체인 5 · 훅과 섀클 3 · 그 밖 4&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;장력 × 안전계수 5 를 넘는 가장 작은 것&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;줄걸이 각도와 와이어로프의 안전계수&lt;/strong&gt;&lt;br&gt;$T = \dfrac{W}{2 \cos \theta}$다. &lt;strong&gt;각도가 벌어질수록 장력이 커진다&lt;/strong&gt; — 60° 면 $W$ 그대로, 75° 면 약 1.93배가 된다. 양중기 달기구의 안전계수는 &lt;strong&gt;달기 와이어로프·체인 5 · 훅과 섀클 3 · 그 밖 4&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;장력 × 안전계수 5를 넘는 가장 작은 것&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8552,7 +8556,7 @@
       </c>
       <c r="AI58" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;방사선투과시험(RT)의 상질 점검&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;RT 는 필름에 비친 그림을 본다&lt;/strong&gt;는 것이 핵심이다. 그래서 점검 항목이 모두 &lt;strong&gt;사진의 선명함과 진하기&lt;/strong&gt;에 관한 것이다. &lt;strong&gt;주파수는 소리(초음파)&lt;/strong&gt;의 값이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;주파수는 초음파탐상 것&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;방사선투과시험(RT)의 상질 점검&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;RT는 필름에 비친 그림을 본다&lt;/strong&gt;는 것이 핵심이다. 그래서 점검 항목이 모두 &lt;strong&gt;사진의 선명함과 진하기&lt;/strong&gt;에 관한 것이다. &lt;strong&gt;주파수는 소리(초음파)&lt;/strong&gt;의 값이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;주파수는 초음파탐상 것&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8641,7 @@
       </c>
       <c r="U59" s="32" t="inlineStr">
         <is>
-          <t>화물중량이 200kgf, 지게차의 중량이 400kgf, 앞바퀴에서 화물의 무게중심까지의 최단거리가 1m일 때 지게차의 무게중심까지 최단거리는 최소 몇 m 를 초과해야하는가?</t>
+          <t>화물중량이 200kgf, 지게차의 중량이 400kgf, 앞바퀴에서 화물의 무게중심까지의 최단거리가 1m일 때 지게차의 무게중심까지 최단거리는 최소 몇 m를 초과해야하는가?</t>
         </is>
       </c>
       <c r="V59" s="32" t="inlineStr"/>
@@ -8671,12 +8675,12 @@
       </c>
       <c r="AG59" s="32" t="inlineStr">
         <is>
-          <t>지게차가 앞으로 넘어지지 않으려면 $M_{1} &amp;lt; M_{2}$ 여야 한다. $200 \times 1 &amp;lt; 400 \times b$ 이므로 $b &amp;gt; 0.5$ [m] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;지게차의 안정조건&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;화물의 모멘트 &lt;/u&gt;$M_{1}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;화물 무게 × 앞바퀴에서 화물 무게중심까지 거리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;앞으로 넘어뜨리려는 힘&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지게차의 모멘트 &lt;/u&gt;$M_{2}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;지게차 무게 × 앞바퀴에서 지게차 무게중심까지 거리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;뒤에서 버티는 힘&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안정조건&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$M_{1} &amp;lt; M_{2}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;버티는 힘이 더 커야 한다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>지게차가 앞으로 넘어지지 않으려면 $M_{1} &amp;lt; M_{2}$ 여야 한다. $200 \times 1 &amp;lt; 400 \times b$이므로 $b &amp;gt; 0.5$ [m]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;지게차의 안정조건&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;화물의 모멘트 &lt;/u&gt;$M_{1}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;화물 무게 × 앞바퀴에서 화물 무게중심까지 거리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;앞으로 넘어뜨리려는 힘&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지게차의 모멘트 &lt;/u&gt;$M_{2}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;지게차 무게 × 앞바퀴에서 지게차 무게중심까지 거리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;뒤에서 버티는 힘&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안정조건&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$M_{1} &amp;lt; M_{2}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;버티는 힘이 더 커야 한다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH59" s="32" t="inlineStr">
         <is>
-          <t>① 0.2 [m] 면 $M_{2} = 80$ 으로 $M_{1} = 200$ 보다 작아 넘어진다.&lt;br&gt;③ 1 [m] 는 조건을 넘지만 「최소」가 아니다.&lt;br&gt;④ 2 [m] 도 최소값이 아니다.</t>
+          <t>① 0.2 [m] 면 $M_{2} = 80$으로 $M_{1} = 200$보다 작아 넘어진다.&lt;br&gt;③ 1 [m]는 조건을 넘지만 「최소」가 아니다.&lt;br&gt;④ 2 [m] 도 최소값이 아니다.</t>
         </is>
       </c>
       <c r="AI59" s="32" t="inlineStr">
@@ -9445,7 +9449,7 @@
       </c>
       <c r="AG65" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;대지전압 150 [V] 를 넘으면&lt;/strong&gt; 반드시 누전차단기를 달아야 한다. 나머지 셋은 생략할 수 있는 경우다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;누전차단기를 생략할 수 있는 경우&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;경우&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;까닭&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;절연물로 피복된 기계기구&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;사람에게 닿지 않는다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;유도전동기의 2차측 전로에 접속된 저항기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;특수한 전로&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2중 절연구조의 기계기구&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;절연이 두 겹&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대지전압 150 [V] 이하&lt;/u&gt;를 물기 없는 곳에&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;초과하면 설치해야 한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비접지식 전로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;대지로 흐르는 길이 없다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;대지전압 150 [V]를 넘으면&lt;/strong&gt; 반드시 누전차단기를 달아야 한다. 나머지 셋은 생략할 수 있는 경우다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;누전차단기를 생략할 수 있는 경우&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;경우&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;까닭&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;절연물로 피복된 기계기구&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;사람에게 닿지 않는다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;유도전동기의 2차측 전로에 접속된 저항기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;특수한 전로&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2중 절연구조의 기계기구&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;절연이 두 겹&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대지전압 150 [V] 이하&lt;/u&gt;를 물기 없는 곳에&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;초과하면 설치해야 한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비접지식 전로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;대지로 흐르는 길이 없다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH65" s="32" t="inlineStr">
@@ -9584,7 +9588,7 @@
       </c>
       <c r="AI66" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;전격 위험도의 결정 인자&lt;/strong&gt;&lt;br&gt;전압은 &lt;strong&gt;인체저항과 함께 전류를 만드는 재료&lt;/strong&gt; 일 뿐, 위험을 결정하는 것은 &lt;strong&gt;실제로 몸에 흐른 전류&lt;/strong&gt;다. 같은 전압이라도 젖어 있으면 전류가 훨씬 커진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;전압이 아니라 전류&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;전격 위험도의 결정 인자&lt;/strong&gt;&lt;br&gt;전압은 &lt;strong&gt;인체저항과 함께 전류를 만드는 재료&lt;/strong&gt;일 뿐, 위험을 결정하는 것은 &lt;strong&gt;실제로 몸에 흐른 전류&lt;/strong&gt;다. 같은 전압이라도 젖어 있으면 전류가 훨씬 커진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;전압이 아니라 전류&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9708,12 +9712,12 @@
       </c>
       <c r="AH67" s="32" t="inlineStr">
         <is>
-          <t>① 0.06초는 지동시간의 오차 범위에 쓰이는 값이다.&lt;br&gt;③ 2 ± 0.3초·50 [V] 는 기준이 아니다.&lt;br&gt;④ 1.5 ± 0.06초는 무접점방식 쪽이며 전압도 25 [V] 이하다.</t>
+          <t>① 0.06초는 지동시간의 오차 범위에 쓰이는 값이다.&lt;br&gt;③ 2 ± 0.3초·50 [V]는 기준이 아니다.&lt;br&gt;④ 1.5 ± 0.06초는 무접점방식 쪽이며 전압도 25 [V] 이하다.</t>
         </is>
       </c>
       <c r="AI67" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;교류 아크 용접기의 자동전격방지장치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;지동시간&lt;/strong&gt;은 &lt;strong&gt;아크가 끊긴 뒤 무부하전압이 25 [V] 아래로 떨어질 때까지 걸리는 시간&lt;/strong&gt;이다. 용접기의 무부하 전압 60~95 [V] 를 그대로 두면 감전 위험이 크기 때문에 낮춘다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1 ± 0.3초에 25 [V] 이하&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;교류 아크 용접기의 자동전격방지장치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;지동시간&lt;/strong&gt;은 &lt;strong&gt;아크가 끊긴 뒤 무부하전압이 25 [V] 아래로 떨어질 때까지 걸리는 시간&lt;/strong&gt;이다. 용접기의 무부하 전압 60~95 [V]를 그대로 두면 감전 위험이 크기 때문에 낮춘다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1 ± 0.3초에 25 [V] 이하&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10086,17 +10090,17 @@
       </c>
       <c r="AG70" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;대지전압 30 [V] 이하&lt;/strong&gt;면 전기위험 방지조치를 하지 않아도 된다. 우리나라의 &lt;strong&gt;안전전압&lt;/strong&gt;이 30 [V] 다.</t>
+          <t>&lt;strong&gt;대지전압 30 [V] 이하&lt;/strong&gt;면 전기위험 방지조치를 하지 않아도 된다. 우리나라의 &lt;strong&gt;안전전압&lt;/strong&gt;이 30 [V]다.</t>
         </is>
       </c>
       <c r="AH70" s="32" t="inlineStr">
         <is>
-          <t>① 24 [V] 는 독일·영국의 안전전압이다.&lt;br&gt;③ 50 [V] 는 네덜란드의 안전전압이며, 누전차단기 시설 기준이기도 하다.&lt;br&gt;④ 100 [V] 는 기준이 아니다.</t>
+          <t>① 24 [V]는 독일·영국의 안전전압이다.&lt;br&gt;③ 50 [V]는 네덜란드의 안전전압이며, 누전차단기 시설 기준이기도 하다.&lt;br&gt;④ 100 [V]는 기준이 아니다.</t>
         </is>
       </c>
       <c r="AI70" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전전압과 충전부 방호&lt;/strong&gt;&lt;br&gt;세 숫자를 갈라 둔다 — &lt;strong&gt;30 [V] 는 안전전압(방호조치 생략)&lt;/strong&gt;, &lt;strong&gt;50 [V] 초과는 누전차단기 시설 대상&lt;/strong&gt;, &lt;strong&gt;150 [V] 초과는 접지 대상&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;우리나라 안전전압은 30 [V]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;안전전압과 충전부 방호&lt;/strong&gt;&lt;br&gt;세 숫자를 갈라 둔다 — &lt;strong&gt;30 [V]는 안전전압(방호조치 생략)&lt;/strong&gt;, &lt;strong&gt;50 [V] 초과는 누전차단기 시설 대상&lt;/strong&gt;, &lt;strong&gt;150 [V] 초과는 접지 대상&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;우리나라 안전전압은 30 [V]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10344,7 +10348,7 @@
       </c>
       <c r="AG72" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;「3종 장소」는 없다&lt;/strong&gt;. 가스 위험장소는 &lt;strong&gt;0종 · 1종 · 2종&lt;/strong&gt; 셋뿐이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;위험장소의 구분&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;장소&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;가스가 있는 정도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;쓸 수 있는 방폭구조&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;0종&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;계속 또는 장시간 존재&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;ia 뿐&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1종&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정상 운전 중 때때로 생김&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;ia · ib · d · p · o · e · m · q&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2종&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이상 시에만 잠깐&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;위의 것 모두 + &lt;u&gt;n&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;「3종 장소」는 없다&lt;/strong&gt;. 가스 위험장소는 &lt;strong&gt;0종 · 1종 · 2종&lt;/strong&gt; 셋뿐이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;위험장소의 구분&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;장소&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;가스가 있는 정도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;쓸 수 있는 방폭구조&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;0종&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;계속 또는 장시간 존재&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;ia뿐&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1종&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정상 운전 중 때때로 생김&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;ia · ib · d · p · o · e · m · q&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2종&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이상 시에만 잠깐&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;위의 것 모두 + &lt;u&gt;n&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH72" s="32" t="inlineStr">
@@ -10473,12 +10477,12 @@
       </c>
       <c r="AG73" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;T2 는 300 [℃] 이하&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;온도등급과 최고표면온도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;등급&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;최고표면온도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;등급&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;최고표면온도&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;450 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;T4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;135 [℃]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;300 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;T5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;100 [℃]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;200 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;T6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;85 [℃]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;T2는 300 [℃] 이하&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;온도등급과 최고표면온도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;등급&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;최고표면온도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;등급&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;최고표면온도&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;450 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;T4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;135 [℃]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;300 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;T5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;100 [℃]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;200 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;T6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;85 [℃]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH73" s="32" t="inlineStr">
         <is>
-          <t>① 135 [℃] 는 T4 다.&lt;br&gt;② 200 [℃] 는 T3 다.&lt;br&gt;④ 450 [℃] 는 T1 이다.</t>
+          <t>① 135 [℃]는 T4다.&lt;br&gt;② 200 [℃]는 T3다.&lt;br&gt;④ 450 [℃]는 T1이다.</t>
         </is>
       </c>
       <c r="AI73" s="32" t="inlineStr">
@@ -10602,17 +10606,17 @@
       </c>
       <c r="AG74" s="32" t="inlineStr">
         <is>
-          <t>$W = \dfrac{1}{2} C V^{2} = \dfrac{1}{2} \times 20 \times 10^{-6} \times ( 2 \times 10^{3} )^{2} = \dfrac{1}{2} \times 20 \times 10^{-6} \times 4 \times 10^{6} = 40$ [J] 이다.</t>
+          <t>$W = \dfrac{1}{2} C V^{2} = \dfrac{1}{2} \times 20 \times 10^{-6} \times ( 2 \times 10^{3} )^{2} = \dfrac{1}{2} \times 20 \times 10^{-6} \times 4 \times 10^{6} = 40$ [J]이다.</t>
         </is>
       </c>
       <c r="AH74" s="32" t="inlineStr">
         <is>
-          <t>② 80 [J] 은 $1 / 2$ 를 곱하지 않은 값이다.&lt;br&gt;③ 400 [J] 은 자릿수가 어긋난다.&lt;br&gt;④ 800 [J] 도 어긋난다.</t>
+          <t>② 80 [J]은 $1 / 2$를 곱하지 않은 값이다.&lt;br&gt;③ 400 [J]은 자릿수가 어긋난다.&lt;br&gt;④ 800 [J] 도 어긋난다.</t>
         </is>
       </c>
       <c r="AI74" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;정전기 에너지 $W = \dfrac{1}{2} C V^{2}$&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;[μF] 는 &lt;/strong&gt;$10^{-6}$&lt;strong&gt;, [kV] 는 &lt;/strong&gt;$10^{3}$이고 &lt;strong&gt;전압은 제곱&lt;/strong&gt; 된다. $1 / 2$ 를 빠뜨려 두 배로 답하는 것이 가장 흔한 실수다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $W = \dfrac{1}{2} C V^{2}$ — &lt;u&gt;1/2 을 잊지 않는다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;정전기 에너지 $W = \dfrac{1}{2} C V^{2}$&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;[μF]는 &lt;/strong&gt;$10^{-6}$&lt;strong&gt;, [kV]는 &lt;/strong&gt;$10^{3}$이고 &lt;strong&gt;전압은 제곱&lt;/strong&gt;된다. $1 / 2$를 빠뜨려 두 배로 답하는 것이 가장 흔한 실수다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $W = \dfrac{1}{2} C V^{2}$ — &lt;u&gt;1/2을 잊지 않는다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10736,12 +10740,12 @@
       </c>
       <c r="AH75" s="32" t="inlineStr">
         <is>
-          <t>① VCB 는 진공 차단기다.&lt;br&gt;② MCCB 는 배선용 차단기다.&lt;br&gt;③ OCB 는 유입 차단기다.</t>
+          <t>① VCB는 진공 차단기다.&lt;br&gt;② MCCB는 배선용 차단기다.&lt;br&gt;③ OCB는 유입 차단기다.</t>
         </is>
       </c>
       <c r="AI75" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;차단기의 종류와 소호 방식&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「기중(氣中)」은 「공기 중」&lt;/strong&gt;이라는 뜻이다. 이름 그대로 옮기면 Air Circuit Breaker 다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;기중 차단기 = ACB&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;차단기의 종류와 소호 방식&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「기중(氣中)」은 「공기 중」&lt;/strong&gt;이라는 뜻이다. 이름 그대로 옮기면 Air Circuit Breaker다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;기중 차단기 = ACB&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10834,7 +10838,11 @@
           <t>전원 ── ㉮ DS ──[ ㉯ OCB ]── ㉰ DS ── 부하</t>
         </is>
       </c>
-      <c r="W76" s="32" t="inlineStr"/>
+      <c r="W76" s="32" t="inlineStr">
+        <is>
+          <t>safe_A_2025_03_074_stem1.png</t>
+        </is>
+      </c>
       <c r="X76" s="32" t="inlineStr">
         <is>
           <t>차단: ㉮→㉯→㉰, 투입: ㉮→㉯→㉰</t>
@@ -11003,7 +11011,7 @@
       </c>
       <c r="AI77" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제319조 — 정전작업 시 잔류전하의 방전&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;커패시터 · 케이블 · 콘덴서&lt;/strong&gt;가 있는 회로는 전원을 끊어도 전하가 남는다. 그래서 정전작업 절차에 &lt;strong&gt;잔류전하 방전&lt;/strong&gt; 단계가 따로 들어 있다. 방전 뒤에는 반드시 &lt;strong&gt;검전기로 확인&lt;/strong&gt; 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;콘덴서가 있으면 잔류전하를 뺀다&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C319%EC%A1%B0" target="_blank"&gt;제319조(정전전로에서의 전기작업)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;① 사업주는 근로자가 노출된 충전부 또는 그 부근에서 작업함으로써 감전될 우려가 있는 경우에는 작업에 들어가기 전에 해당 전로를 차단하여야 한다. 다만, 다음 각 호의 경우에는 그러하지 아니하다.&lt;br&gt; 1. 생명유지장치, 비상경보설비, 폭발위험장소의 환기설비, 비상조명설비 등의 장치ㆍ설비의 가동이 중지되어 사고의 위험이 증가되는 경우&lt;br&gt; 2. 기기의 설계상 또는 작동상 제한으로 전로차단이 불가능한 경우&lt;br&gt; 3. 감전, 아크 등으로 인한 화상, 화재ㆍ폭발의 위험이 없는 것으로 확인된 경우&lt;br&gt;② 제1항의 전로 차단은 다음 각 호의 절차에 따라 시행하여야 한다.&lt;br&gt; 1. 전기기기등에 공급되는 모든 전원을 관련 도면, 배선도 등으로 확인할 것&lt;br&gt; 2. 전원을 차단한 후 각 단로기 등을 개방하고 확인할 것&lt;br&gt; 3. 차단장치나 단로기 등에 잠금장치 및 꼬리표를 부착할 것&lt;br&gt; 4. 개로된 전로에서 유도전압 또는 전기에너지가 축적되어 근로자에게 전기위험을 끼칠 수 있는 전기기기등은 접촉하기 전에 잔류전하를 완전히 방전시킬 것&lt;br&gt; 5. 검전기를 이용하여 작업 대상 기기가 충전되었는지를 확인할 것&lt;br&gt; 6. 전기기기등이 다른 노출 충전부와의 접촉, 유도 또는 예비동력원의 역송전 등으로 전압이 발생할 우려가 있는 경우에는 충분한 용량을 가진 단락 접지기구를 이용하여 접지할 것&lt;br&gt;▶ ③ 사업주는 제1항 각 호 외의 부분 본문에 따른 작업 중 또는 작업을 마친 후 전원을 공급하는 경우에는 작업에 종사하는 근로자 또는 그 인근에서 작업하거나 정전된 전기기기등(고정 설치된 것으로 한정한다)과 접촉할 우려가 있는 근로자에게 감전의 위험이 없도록 다음 각 호의 사항을 준수하여야 한다.&lt;br&gt; 1. 작업기구, 단락 접지기구 등을 제거하고 전기기기등이 안전하게 통전될 수 있는지를 확인할 것&lt;br&gt; 2. 모든 작업자가 작업이 완료된 전기기기등에서 떨어져 있는지를 확인할 것&lt;br&gt; 3. 잠금장치와 꼬리표는 설치한 근로자가 직접 철거할 것&lt;br&gt; 4. 모든 이상 유무를 확인한 후 전기기기등의 전원을 투입할 것&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제319조 — 정전작업 시 잔류전하의 방전&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;커패시터 · 케이블 · 콘덴서&lt;/strong&gt;가 있는 회로는 전원을 끊어도 전하가 남는다. 그래서 정전작업 절차에 &lt;strong&gt;잔류전하 방전&lt;/strong&gt; 단계가 따로 들어 있다. 방전 뒤에는 반드시 &lt;strong&gt;검전기로 확인&lt;/strong&gt;한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;콘덴서가 있으면 잔류전하를 뺀다&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C319%EC%A1%B0" target="_blank"&gt;제319조(정전전로에서의 전기작업)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;① 사업주는 근로자가 노출된 충전부 또는 그 부근에서 작업함으로써 감전될 우려가 있는 경우에는 작업에 들어가기 전에 해당 전로를 차단하여야 한다. 다만, 다음 각 호의 경우에는 그러하지 아니하다.&lt;br&gt; 1. 생명유지장치, 비상경보설비, 폭발위험장소의 환기설비, 비상조명설비 등의 장치ㆍ설비의 가동이 중지되어 사고의 위험이 증가되는 경우&lt;br&gt; 2. 기기의 설계상 또는 작동상 제한으로 전로차단이 불가능한 경우&lt;br&gt; 3. 감전, 아크 등으로 인한 화상, 화재ㆍ폭발의 위험이 없는 것으로 확인된 경우&lt;br&gt;② 제1항의 전로 차단은 다음 각 호의 절차에 따라 시행하여야 한다.&lt;br&gt; 1. 전기기기등에 공급되는 모든 전원을 관련 도면, 배선도 등으로 확인할 것&lt;br&gt; 2. 전원을 차단한 후 각 단로기 등을 개방하고 확인할 것&lt;br&gt; 3. 차단장치나 단로기 등에 잠금장치 및 꼬리표를 부착할 것&lt;br&gt; 4. 개로된 전로에서 유도전압 또는 전기에너지가 축적되어 근로자에게 전기위험을 끼칠 수 있는 전기기기등은 접촉하기 전에 잔류전하를 완전히 방전시킬 것&lt;br&gt; 5. 검전기를 이용하여 작업 대상 기기가 충전되었는지를 확인할 것&lt;br&gt; 6. 전기기기등이 다른 노출 충전부와의 접촉, 유도 또는 예비동력원의 역송전 등으로 전압이 발생할 우려가 있는 경우에는 충분한 용량을 가진 단락 접지기구를 이용하여 접지할 것&lt;br&gt;▶ ③ 사업주는 제1항 각 호 외의 부분 본문에 따른 작업 중 또는 작업을 마친 후 전원을 공급하는 경우에는 작업에 종사하는 근로자 또는 그 인근에서 작업하거나 정전된 전기기기등(고정 설치된 것으로 한정한다)과 접촉할 우려가 있는 근로자에게 감전의 위험이 없도록 다음 각 호의 사항을 준수하여야 한다.&lt;br&gt; 1. 작업기구, 단락 접지기구 등을 제거하고 전기기기등이 안전하게 통전될 수 있는지를 확인할 것&lt;br&gt; 2. 모든 작업자가 작업이 완료된 전기기기등에서 떨어져 있는지를 확인할 것&lt;br&gt; 3. 잠금장치와 꼬리표는 설치한 근로자가 직접 철거할 것&lt;br&gt; 4. 모든 이상 유무를 확인한 후 전기기기등의 전원을 투입할 것&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -11127,12 +11135,12 @@
       </c>
       <c r="AH78" s="32" t="inlineStr">
         <is>
-          <t>② ACB 는 진공이 아니라 대기 중에서 차단한다 — 진공은 VCB 다.&lt;br&gt;③ DS 는 대용량 부하를 개폐하지 못한다.&lt;br&gt;④ 이상전압을 대지로 방전시키는 것은 피뢰기이며, 피뢰침은 직격뢰를 받는 것이다.</t>
+          <t>② ACB는 진공이 아니라 대기 중에서 차단한다 — 진공은 VCB다.&lt;br&gt;③ DS는 대용량 부하를 개폐하지 못한다.&lt;br&gt;④ 이상전압을 대지로 방전시키는 것은 피뢰기이며, 피뢰침은 직격뢰를 받는 것이다.</t>
         </is>
       </c>
       <c r="AI78" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;차단기와 단로기의 차이&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;CB 는 끊을 수 있고 DS 는 끊을 수 없다&lt;/strong&gt;. 이 한 줄이 74번과 76번을 함께 푼다. &lt;strong&gt;피뢰기(기기 보호)와 피뢰침(건물 보호)&lt;/strong&gt;도 갈라 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;CB 는 부하전류를 끊는다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;차단기와 단로기의 차이&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;CB는 끊을 수 있고 DS는 끊을 수 없다&lt;/strong&gt;. 이 한 줄이 74번과 76번을 함께 푼다. &lt;strong&gt;피뢰기(기기 보호)와 피뢰침(건물 보호)&lt;/strong&gt;도 갈라 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;CB는 부하전류를 끊는다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11638,17 +11646,17 @@
       </c>
       <c r="AG82" s="32" t="inlineStr">
         <is>
-          <t>$V = 9 \times 10^{9} \times \dfrac{Q}{r}$ 다. $r = 6 {,} 367 \times 10^{3}$ [m] 이므로 $V = 9 \times 10^{9} \times 1 / ( 6.367 \times 10^{6} ) \fallingdotseq 1 {,} 414$ [V] 다.</t>
+          <t>$V = 9 \times 10^{9} \times \dfrac{Q}{r}$다. $r = 6 {,} 367 \times 10^{3}$ [m]이므로 $V = 9 \times 10^{9} \times 1 / ( 6.367 \times 10^{6} ) \fallingdotseq 1 {,} 414$ [V]다.</t>
         </is>
       </c>
       <c r="AH82" s="32" t="inlineStr">
         <is>
-          <t>② 2,828 [V] 는 반지름을 절반으로 잡았을 때다.&lt;br&gt;③ $9 \times 10^{4}$ [V] 는 자릿수가 어긋난다.&lt;br&gt;④ $9 \times 10^{9}$ [V] 는 반지름으로 나누지 않은 값이다.</t>
+          <t>② 2,828 [V]는 반지름을 절반으로 잡았을 때다.&lt;br&gt;③ $9 \times 10^{4}$ [V]는 자릿수가 어긋난다.&lt;br&gt;④ $9 \times 10^{9}$ [V]는 반지름으로 나누지 않은 값이다.</t>
         </is>
       </c>
       <c r="AI82" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;도체구의 전위&lt;/strong&gt;&lt;br&gt;$V = \dfrac{1}{4 \pi \varepsilon_{0}} \times \dfrac{Q}{r} = 9 \times 10^{9} \times \dfrac{Q}{r}$ 다. &lt;strong&gt;반지름을 [m] 로 바꾸는 것&lt;/strong&gt;이 실수하기 쉬운 자리다 — 6,367 [km] 는 $6.367 \times 10^{6}$ [m] 다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $V = 9 \times 10^{9} Q / r$ — &lt;u&gt;반지름은 미터로&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;도체구의 전위&lt;/strong&gt;&lt;br&gt;$V = \dfrac{1}{4 \pi \varepsilon_{0}} \times \dfrac{Q}{r} = 9 \times 10^{9} \times \dfrac{Q}{r}$다. &lt;strong&gt;반지름을 [m]로 바꾸는 것&lt;/strong&gt;이 실수하기 쉬운 자리다 — 6,367 [km]는 $6.367 \times 10^{6}$ [m]다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $V = 9 \times 10^{9} Q / r$ — &lt;u&gt;반지름은 미터로&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11767,17 +11775,17 @@
       </c>
       <c r="AG83" s="32" t="inlineStr">
         <is>
-          <t>물의 양은 $10 - 6.8 = 3.2$ [kg] 이다. &lt;strong&gt;건량 기준&lt;/strong&gt;은 &lt;strong&gt;마른 고체의 무게로 나눈다&lt;/strong&gt;는 뜻이므로 $3.2 / 6.8 \fallingdotseq 0.47$ 이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;건량 기준과 습량 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;여기서는&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;건량 기준&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{물의 무게}}{\text{마른 고체의 무게}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$3.2 / 6.8 = 0.47$&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;습량 기준&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{물의 무게}}{\text{젖은 재료 전체 무게}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$3.2 / 10 = 0.32$&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>물의 양은 $10 - 6.8 = 3.2$ [kg]이다. &lt;strong&gt;건량 기준&lt;/strong&gt;은 &lt;strong&gt;마른 고체의 무게로 나눈다&lt;/strong&gt;는 뜻이므로 $3.2 / 6.8 \fallingdotseq 0.47$이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;건량 기준과 습량 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;여기서는&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;건량 기준&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{물의 무게}}{\text{마른 고체의 무게}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$3.2 / 6.8 = 0.47$&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;습량 기준&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{물의 무게}}{\text{젖은 재료 전체 무게}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$3.2 / 10 = 0.32$&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH83" s="32" t="inlineStr">
         <is>
-          <t>① 0.25 는 계산과 맞지 않는다.&lt;br&gt;② 0.36 도 맞지 않는다.&lt;br&gt;④ 0.58 도 맞지 않는다.</t>
+          <t>① 0.25는 계산과 맞지 않는다.&lt;br&gt;② 0.36 도 맞지 않는다.&lt;br&gt;④ 0.58 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI83" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;함수율의 두 가지 기준&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;분모가 무엇인가&lt;/strong&gt;로 갈린다. &lt;strong&gt;건량 기준은 마른 고체&lt;/strong&gt;, &lt;strong&gt;습량 기준은 젖은 전체&lt;/strong&gt;다. 건량 기준은 &lt;strong&gt;1 을 넘을 수도&lt;/strong&gt; 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;건량 기준은 마른 무게로 나눈다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;함수율의 두 가지 기준&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;분모가 무엇인가&lt;/strong&gt;로 갈린다. &lt;strong&gt;건량 기준은 마른 고체&lt;/strong&gt;, &lt;strong&gt;습량 기준은 젖은 전체&lt;/strong&gt;다. 건량 기준은 &lt;strong&gt;1을 넘을 수도&lt;/strong&gt; 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;건량 기준은 마른 무게로 나눈다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12035,7 +12043,7 @@
       </c>
       <c r="AI85" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;자연발화의 조건&lt;/strong&gt;&lt;br&gt;자연발화는 &lt;strong&gt;발열 &amp;gt; 방열&lt;/strong&gt; 일 때 일어난다. &lt;strong&gt;열전도율과 공기 유통만 「작을수록」&lt;/strong&gt;이고 나머지는 「클수록·높을수록」이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;고온 · 다습 · 넓은 표면 · 낮은 열전도율&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;자연발화의 조건&lt;/strong&gt;&lt;br&gt;자연발화는 &lt;strong&gt;발열 &amp;gt; 방열&lt;/strong&gt;일 때 일어난다. &lt;strong&gt;열전도율과 공기 유통만 「작을수록」&lt;/strong&gt;이고 나머지는 「클수록·높을수록」이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;고온 · 다습 · 넓은 표면 · 낮은 열전도율&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12154,7 +12162,7 @@
       </c>
       <c r="AG86" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;칼륨&lt;/strong&gt;이다. $2 K + 2 H_{2} O \rightarrow 2 \mathrm{KOH} + H_{2}$ 로 &lt;strong&gt;수소&lt;/strong&gt;를 내며 격렬히 발열한다.</t>
+          <t>&lt;strong&gt;칼륨&lt;/strong&gt;이다. $2 K + 2 H_{2} O \rightarrow 2 \mathrm{KOH} + H_{2}$로 &lt;strong&gt;수소&lt;/strong&gt;를 내며 격렬히 발열한다.</t>
         </is>
       </c>
       <c r="AH86" s="32" t="inlineStr">
@@ -12283,17 +12291,17 @@
       </c>
       <c r="AG87" s="32" t="inlineStr">
         <is>
-          <t>$C_{3} H_{8} + 5 O_{2} \rightarrow 3 CO_{2} + 4 H_{2} O$ 이므로 산소의 양론계수는 5 다. $\mathrm{MOC} = 2.2 \times 5 = 11.0$ [vol%] 다.</t>
+          <t>$C_{3} H_{8} + 5 O_{2} \rightarrow 3 CO_{2} + 4 H_{2} O$이므로 산소의 양론계수는 5다. $\mathrm{MOC} = 2.2 \times 5 = 11.0$ [vol%]다.</t>
         </is>
       </c>
       <c r="AH87" s="32" t="inlineStr">
         <is>
-          <t>① 5.0 [vol%] 는 양론계수만 쓴 값이다.&lt;br&gt;② 7.0 [vol%] 는 계산과 맞지 않는다.&lt;br&gt;③ 9.0 [vol%] 도 맞지 않는다.</t>
+          <t>① 5.0 [vol%]는 양론계수만 쓴 값이다.&lt;br&gt;② 7.0 [vol%]는 계산과 맞지 않는다.&lt;br&gt;③ 9.0 [vol%] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI87" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;최소산소농도(MOC)&lt;/strong&gt;&lt;br&gt;$\mathrm{MOC} = \text{폭발하한계} \times ( n + \dfrac{m}{4} )$ 다. 프로판은 $3 + 8 / 4 = 5$ 다. 실무에서는 &lt;strong&gt;MOC 보다 4 [%] 정도 더 낮게&lt;/strong&gt; 잡아 불활성화한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $\mathrm{MOC} = \mathrm{LFL} \times \text{산소 양론계수}$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;최소산소농도(MOC)&lt;/strong&gt;&lt;br&gt;$\mathrm{MOC} = \text{폭발하한계} \times ( n + \dfrac{m}{4} )$다. 프로판은 $3 + 8 / 4 = 5$다. 실무에서는 &lt;strong&gt;MOC보다 4 [%] 정도 더 낮게&lt;/strong&gt; 잡아 불활성화한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $\mathrm{MOC} = \mathrm{LFL} \times \text{산소 양론계수}$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12541,7 +12549,7 @@
       </c>
       <c r="AG89" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;인화점과 발화점은 반드시 나란히 가지 않는다&lt;/strong&gt;. 이황화탄소는 인화점 −30 [℃] 로 매우 낮지만 발화점은 100 [℃] 로 낮은 편이고, 반대로 &lt;strong&gt;아세틸렌은 인화점이 매우 낮지만 발화점은 305 [℃]&lt;/strong&gt;로 높다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;인화점과 발화점은 따로 논다&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;물질&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;인화점&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;발화점&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이황화탄소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;−30 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;100 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;둘 다 낮다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;디에틸에테르&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;−45 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;180 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;인화점은 더 낮은데 발화점은 높다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;휘발유&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;−43 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;약 300 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;등유&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;40 ~ 70 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;약 210 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;인화점은 높은데 발화점은 낮다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;인화점과 발화점은 반드시 나란히 가지 않는다&lt;/strong&gt;. 이황화탄소는 인화점 −30 [℃]로 매우 낮지만 발화점은 100 [℃]로 낮은 편이고, 반대로 &lt;strong&gt;아세틸렌은 인화점이 매우 낮지만 발화점은 305 [℃]&lt;/strong&gt;로 높다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;인화점과 발화점은 따로 논다&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;물질&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;인화점&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;발화점&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이황화탄소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;−30 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;100 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;둘 다 낮다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;디에틸에테르&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;−45 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;180 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;인화점은 더 낮은데 발화점은 높다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;휘발유&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;−43 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;약 300 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;등유&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;40 ~ 70 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;약 210 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;인화점은 높은데 발화점은 낮다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH89" s="32" t="inlineStr">
@@ -12675,7 +12683,7 @@
       </c>
       <c r="AH90" s="32" t="inlineStr">
         <is>
-          <t>① 2 ~ 10.4 [%] 는 프로판·아세톤 쪽 범위다.&lt;br&gt;③ 2.5 ~ 15 [%] 도 아니다.&lt;br&gt;④ 1.5 ~ 7.8 [%] 는 가솔린 쪽에 가깝다.</t>
+          <t>① 2 ~ 10.4 [%]는 프로판·아세톤 쪽 범위다.&lt;br&gt;③ 2.5 ~ 15 [%] 도 아니다.&lt;br&gt;④ 1.5 ~ 7.8 [%]는 가솔린 쪽에 가깝다.</t>
         </is>
       </c>
       <c r="AI90" s="32" t="inlineStr">
@@ -13186,7 +13194,7 @@
       </c>
       <c r="AG94" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;일산화탄소&lt;/strong&gt;다. &lt;strong&gt;폭발범위 12.5 ~ 74 [vol%] 의 가연성&lt;/strong&gt; 이면서 &lt;strong&gt;허용농도 30 [ppm] 의 독성&lt;/strong&gt;이다.</t>
+          <t>&lt;strong&gt;일산화탄소&lt;/strong&gt;다. &lt;strong&gt;폭발범위 12.5 ~ 74 [vol%]의 가연성&lt;/strong&gt; 이면서 &lt;strong&gt;허용농도 30 [ppm]의 독성&lt;/strong&gt;이다.</t>
         </is>
       </c>
       <c r="AH94" s="32" t="inlineStr">
@@ -13444,7 +13452,7 @@
       </c>
       <c r="AG96" s="32" t="inlineStr">
         <is>
-          <t>자동압력조절밸브와 안전밸브는 &lt;strong&gt;직렬이 아니라 병렬&lt;/strong&gt;로 연결되어야 한다. 직렬이면 한쪽이 막혔을 때 압력을 뺄 길이 사라진다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;차단밸브를 달 수 있는 예외 (규칙 제266조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;경우&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;인접한 화학설비에 안전밸브등이 각각 설치되고 연결배관에 차단밸브가 없는 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전밸브등이 복수방식으로 설치된 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;파열판과 안전밸브를 병렬로 설치한 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;배출용량의 1/2 이상인 자동압력조절밸브와 안전밸브등이 병렬로 연결된 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1/4 이 아니라 1/2, 직렬이 아니라 병렬&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;열팽창에 의한 압력을 낮추려는 목적인 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하나의 플레어 스택에 둘 이상의 단위공정 안전밸브등이 연결된 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>자동압력조절밸브와 안전밸브는 &lt;strong&gt;직렬이 아니라 병렬&lt;/strong&gt;로 연결되어야 한다. 직렬이면 한쪽이 막혔을 때 압력을 뺄 길이 사라진다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;차단밸브를 달 수 있는 예외 (규칙 제266조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;경우&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;인접한 화학설비에 안전밸브등이 각각 설치되고 연결배관에 차단밸브가 없는 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전밸브등이 복수방식으로 설치된 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;파열판과 안전밸브를 병렬로 설치한 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;배출용량의 1/2 이상인 자동압력조절밸브와 안전밸브등이 병렬로 연결된 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1/4이 아니라 1/2, 직렬이 아니라 병렬&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;열팽창에 의한 압력을 낮추려는 목적인 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하나의 플레어 스택에 둘 이상의 단위공정 안전밸브등이 연결된 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH96" s="32" t="inlineStr">
@@ -13454,7 +13462,7 @@
       </c>
       <c r="AI96" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제266조 — 차단밸브의 설치 금지&lt;/strong&gt;&lt;br&gt;예외의 공통점은 하나 — &lt;strong&gt;하나를 잠가도 압력을 뺄 다른 길이 남아 있는가&lt;/strong&gt;. &lt;strong&gt;직렬이면 길이 하나뿐&lt;/strong&gt;이라 예외가 될 수 없다. &lt;strong&gt;1/4 과 1/2, 직렬과 병렬&lt;/strong&gt; 두 군데가 바뀌어 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1/2 이상, 병렬로&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C266%EC%A1%B0" target="_blank"&gt;제266조(차단밸브의 설치 금지)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;사업주는 안전밸브등의 전단ㆍ후단에 차단밸브를 설치해서는 아니 된다. 다만, 다음 각 호의 어느 하나에 해당하는 경우에는 자물쇠형 또는 이에 준하는 형식의 차단밸브를 설치할 수 있다.&lt;br&gt; 1. 인접한 화학설비 및 그 부속설비에 안전밸브등이 각각 설치되어 있고, 해당 화학설비 및 그 부속설비의 연결배관에 차단밸브가 없는 경우&lt;br&gt;▶  2. 안전밸브등의 배출용량의 2분의 1 이상에 해당하는 용량의 자동압력조절밸브(구동용 동력원의 공급을 차단하는 경우 열리는 구조인 것으로 한정한다)와 안전밸브등이 병렬로 연결된 경우&lt;br&gt; 3. 화학설비 및 그 부속설비에 안전밸브등이 복수방식으로 설치되어 있는 경우&lt;br&gt; 4. 예비용 설비를 설치하고 각각의 설비에 안전밸브등이 설치되어 있는 경우&lt;br&gt; 5. 열팽창에 의하여 상승된 압력을 낮추기 위한 목적으로 안전밸브가 설치된 경우&lt;br&gt; 6. 하나의 플레어 스택(flare stack)에 둘 이상의 단위공정의 플레어 헤더(flare header)를 연결하여 사용하는 경우로서 각각의 단위공정의 플레어헤더에 설치된 차단밸브의 열림ㆍ닫힘 상태를 중앙제어실에서 알 수 있도록 조치한 경우&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제266조 — 차단밸브의 설치 금지&lt;/strong&gt;&lt;br&gt;예외의 공통점은 하나 — &lt;strong&gt;하나를 잠가도 압력을 뺄 다른 길이 남아 있는가&lt;/strong&gt;. &lt;strong&gt;직렬이면 길이 하나뿐&lt;/strong&gt;이라 예외가 될 수 없다. &lt;strong&gt;1/4과 1/2, 직렬과 병렬&lt;/strong&gt; 두 군데가 바뀌어 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1/2 이상, 병렬로&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C266%EC%A1%B0" target="_blank"&gt;제266조(차단밸브의 설치 금지)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;사업주는 안전밸브등의 전단ㆍ후단에 차단밸브를 설치해서는 아니 된다. 다만, 다음 각 호의 어느 하나에 해당하는 경우에는 자물쇠형 또는 이에 준하는 형식의 차단밸브를 설치할 수 있다.&lt;br&gt; 1. 인접한 화학설비 및 그 부속설비에 안전밸브등이 각각 설치되어 있고, 해당 화학설비 및 그 부속설비의 연결배관에 차단밸브가 없는 경우&lt;br&gt;▶  2. 안전밸브등의 배출용량의 2분의 1 이상에 해당하는 용량의 자동압력조절밸브(구동용 동력원의 공급을 차단하는 경우 열리는 구조인 것으로 한정한다)와 안전밸브등이 병렬로 연결된 경우&lt;br&gt; 3. 화학설비 및 그 부속설비에 안전밸브등이 복수방식으로 설치되어 있는 경우&lt;br&gt; 4. 예비용 설비를 설치하고 각각의 설비에 안전밸브등이 설치되어 있는 경우&lt;br&gt; 5. 열팽창에 의하여 상승된 압력을 낮추기 위한 목적으로 안전밸브가 설치된 경우&lt;br&gt; 6. 하나의 플레어 스택(flare stack)에 둘 이상의 단위공정의 플레어 헤더(flare header)를 연결하여 사용하는 경우로서 각각의 단위공정의 플레어헤더에 설치된 차단밸브의 열림ㆍ닫힘 상태를 중앙제어실에서 알 수 있도록 조치한 경우&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -13707,7 +13715,7 @@
       </c>
       <c r="AH98" s="32" t="inlineStr">
         <is>
-          <t>② 목재는 분해연소다.&lt;br&gt;③ TNT 는 자기연소다.&lt;br&gt;④ 목탄은 표면연소다.</t>
+          <t>② 목재는 분해연소다.&lt;br&gt;③ TNT는 자기연소다.&lt;br&gt;④ 목탄은 표면연소다.</t>
         </is>
       </c>
       <c r="AI98" s="32" t="inlineStr">
@@ -13831,7 +13839,7 @@
       </c>
       <c r="AG99" s="32" t="inlineStr">
         <is>
-          <t>용기의 온도는 &lt;strong&gt;섭씨 40도 이하&lt;/strong&gt;로 유지해야 한다. 65도가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;가스 용기 취급 시의 준수사항 (규칙 제234조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;준수사항&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;용기의 온도를 40 [℃] 이하로 유지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;65 [℃] 가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전도의 위험이 없도록 할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;충격을 가하지 않을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;운반할 때는 캡을 씌울 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사용할 때는 용기의 마개에 부착된 오물·석유류·유지류를 제거할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;밸브의 개폐는 서서히 할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;용해아세틸렌의 용기는 세워 둘 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;눕히면 아세톤이 흘러나온다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사용 전·후에 반드시 잔량을 확인할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>용기의 온도는 &lt;strong&gt;섭씨 40도 이하&lt;/strong&gt;로 유지해야 한다. 65도가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;가스 용기 취급 시의 준수사항 (규칙 제234조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;준수사항&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;용기의 온도를 40 [℃] 이하로 유지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;65 [℃]가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전도의 위험이 없도록 할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;충격을 가하지 않을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;운반할 때는 캡을 씌울 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사용할 때는 용기의 마개에 부착된 오물·석유류·유지류를 제거할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;밸브의 개폐는 서서히 할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;용해아세틸렌의 용기는 세워 둘 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;눕히면 아세톤이 흘러나온다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사용 전·후에 반드시 잔량을 확인할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH99" s="32" t="inlineStr">
@@ -13970,7 +13978,7 @@
       </c>
       <c r="AI100" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;물과의 발열반응과 흡열반응&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;물과 만나는 대부분의 위험물은 발열&lt;/strong&gt; 한다. &lt;strong&gt;질산암모늄은 드물게 흡열&lt;/strong&gt;이라 시험에 자주 나온다. 다만 질산암모늄 자체는 &lt;strong&gt;가열하면 폭발하는 산화성 고체&lt;/strong&gt;라 위험하지 않은 것은 아니다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;질산암모늄만 흡열&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;물과의 발열반응과 흡열반응&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;물과 만나는 대부분의 위험물은 발열&lt;/strong&gt;한다. &lt;strong&gt;질산암모늄은 드물게 흡열&lt;/strong&gt;이라 시험에 자주 나온다. 다만 질산암모늄 자체는 &lt;strong&gt;가열하면 폭발하는 산화성 고체&lt;/strong&gt;라 위험하지 않은 것은 아니다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;질산암모늄만 흡열&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14089,7 +14097,7 @@
       </c>
       <c r="AG101" s="32" t="inlineStr">
         <is>
-          <t>마그네슘 화재에는 &lt;strong&gt;이산화탄소도 쓸 수 없다&lt;/strong&gt;. $2 \mathrm{Mg} + CO_{2} \rightarrow 2 \mathrm{MgO} + C$ 로 &lt;strong&gt;이산화탄소를 분해하며 계속 탄다&lt;/strong&gt;. &lt;strong&gt;건조사나 팽창질석&lt;/strong&gt;으로 덮어야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;금속화재(D급)에 쓸 수 없는 소화약제&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;약제&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;왜 안 되나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수소를 내며 폭발&lt;/u&gt; 한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이산화탄소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;금속이 CO₂ 를 분해&lt;/u&gt; 하며 탄다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;할론&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;금속과 반응&lt;/u&gt; 한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;포&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;물이 들어 있다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;건조사 · 팽창질석 · 금속화재용 분말&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;덮어서 산소를 끊는다&lt;/u&gt; — 이것만 가능&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>마그네슘 화재에는 &lt;strong&gt;이산화탄소도 쓸 수 없다&lt;/strong&gt;. $2 \mathrm{Mg} + CO_{2} \rightarrow 2 \mathrm{MgO} + C$로 &lt;strong&gt;이산화탄소를 분해하며 계속 탄다&lt;/strong&gt;. &lt;strong&gt;건조사나 팽창질석&lt;/strong&gt;으로 덮어야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;금속화재(D급)에 쓸 수 없는 소화약제&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;약제&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;왜 안 되나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수소를 내며 폭발&lt;/u&gt;한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이산화탄소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;금속이 CO₂ 를 분해&lt;/u&gt;하며 탄다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;할론&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;금속과 반응&lt;/u&gt;한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;포&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;물이 들어 있다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;건조사 · 팽창질석 · 금속화재용 분말&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;덮어서 산소를 끊는다&lt;/u&gt; — 이것만 가능&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH101" s="32" t="inlineStr">
@@ -14218,7 +14226,7 @@
       </c>
       <c r="AG102" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;니트로셀룰로오스는 오히려 물이나 알코올로 적셔 보관&lt;/strong&gt; 한다. 건조하면 마찰과 충격만으로도 분해·발화하기 때문이다.</t>
+          <t>&lt;strong&gt;니트로셀룰로오스는 오히려 물이나 알코올로 적셔 보관&lt;/strong&gt;한다. 건조하면 마찰과 충격만으로도 분해·발화하기 때문이다.</t>
         </is>
       </c>
       <c r="AH102" s="32" t="inlineStr">
@@ -14485,12 +14493,12 @@
       </c>
       <c r="AH104" s="32" t="inlineStr">
         <is>
-          <t>① 50 [kgf] 는 어느 칸에도 없다.&lt;br&gt;② 100 [kgf] 도 없다.&lt;br&gt;④ 150 [kgf] 는 10 [cm] 매듭 없는 방망의 폐기 값이다.</t>
+          <t>① 50 [kgf]는 어느 칸에도 없다.&lt;br&gt;② 100 [kgf] 도 없다.&lt;br&gt;④ 150 [kgf]는 10 [cm] 매듭 없는 방망의 폐기 값이다.</t>
         </is>
       </c>
       <c r="AI104" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;추락재해방지 표준안전작업지침 — 방망사의 인장강도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;5 [cm] 는 매듭 있는 것만&lt;/strong&gt; 기준이 있다. 그물코가 작을수록 &lt;strong&gt;한 가닥에 걸리는 힘이 작아&lt;/strong&gt; 요구 강도도 낮다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;5 [cm] 매듭 — 신품 110, 폐기 60&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;추락재해방지 표준안전작업지침 — 방망사의 인장강도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;5 [cm]는 매듭 있는 것만&lt;/strong&gt; 기준이 있다. 그물코가 작을수록 &lt;strong&gt;한 가닥에 걸리는 힘이 작아&lt;/strong&gt; 요구 강도도 낮다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;5 [cm] 매듭 — 신품 110, 폐기 60&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14609,12 +14617,12 @@
       </c>
       <c r="AG105" s="32" t="inlineStr">
         <is>
-          <t>끊어진 소선이 &lt;strong&gt;10 [%] 미만&lt;/strong&gt;이면 쓸 수 있다. 5 [%] 는 기준 안이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;와이어로프의 사용 금지 기준 (규칙 제63조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;사용할 수 없는 것&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이음매가 있는 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;무조건 금지&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;한 꼬임에서 끊어진 소선의 수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [%] 이상&lt;/u&gt; — 5 [%] 는 괜찮다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지름의 감소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;공칭지름의 7 [%] 초과&lt;/u&gt; — 10 [%] 는 금지&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;꼬인 것 · 심하게 변형되거나 부식된 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;열과 전기충격에 의해 손상된 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>끊어진 소선이 &lt;strong&gt;10 [%] 미만&lt;/strong&gt;이면 쓸 수 있다. 5 [%]는 기준 안이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;와이어로프의 사용 금지 기준 (규칙 제63조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;사용할 수 없는 것&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이음매가 있는 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;무조건 금지&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;한 꼬임에서 끊어진 소선의 수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [%] 이상&lt;/u&gt; — 5 [%]는 괜찮다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지름의 감소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;공칭지름의 7 [%] 초과&lt;/u&gt; — 10 [%]는 금지&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;꼬인 것 · 심하게 변형되거나 부식된 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;열과 전기충격에 의해 손상된 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH105" s="32" t="inlineStr">
         <is>
-          <t>① 이음매가 있는 것은 무조건 쓸 수 없다.&lt;br&gt;③ 지름 감소가 공칭지름의 10 [%] 면 7 [%] 를 넘어 쓸 수 없다.&lt;br&gt;④ 열과 전기충격에 손상된 것도 쓸 수 없다.</t>
+          <t>① 이음매가 있는 것은 무조건 쓸 수 없다.&lt;br&gt;③ 지름 감소가 공칭지름의 10 [%] 면 7 [%]를 넘어 쓸 수 없다.&lt;br&gt;④ 열과 전기충격에 손상된 것도 쓸 수 없다.</t>
         </is>
       </c>
       <c r="AI105" s="32" t="inlineStr">
@@ -14743,7 +14751,7 @@
       </c>
       <c r="AH106" s="32" t="inlineStr">
         <is>
-          <t>① 200 [kgf] 는 10 [cm] 매듭 있는 방망의 신품 값이다.&lt;br&gt;② 100 [kgf] 는 어느 칸에도 없다.&lt;br&gt;④ 30 [kgf] 도 없다.</t>
+          <t>① 200 [kgf]는 10 [cm] 매듭 있는 방망의 신품 값이다.&lt;br&gt;② 100 [kgf]는 어느 칸에도 없다.&lt;br&gt;④ 30 [kgf] 도 없다.</t>
         </is>
       </c>
       <c r="AI106" s="32" t="inlineStr">
@@ -15125,7 +15133,7 @@
       </c>
       <c r="AG109" s="32" t="inlineStr">
         <is>
-          <t>작업발판의 폭은 &lt;strong&gt;40 [cm] 이상&lt;/strong&gt;이다. 30 [cm] 는 &lt;strong&gt;사다리식 통로&lt;/strong&gt;의 폭이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;말비계의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지주부재와 수평면의 기울기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;75° 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;높이 2 [m] 초과 시 작업발판 폭&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;40 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;30 [cm] 가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지주부재 사이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;보조부재&lt;/u&gt; 설치&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;다리가 벌어지지 않게&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;밑부분&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;미끄럼 방지장치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>작업발판의 폭은 &lt;strong&gt;40 [cm] 이상&lt;/strong&gt;이다. 30 [cm]는 &lt;strong&gt;사다리식 통로&lt;/strong&gt;의 폭이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;말비계의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지주부재와 수평면의 기울기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;75° 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;높이 2 [m] 초과 시 작업발판 폭&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;40 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;30 [cm]가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지주부재 사이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;보조부재&lt;/u&gt; 설치&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;다리가 벌어지지 않게&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;밑부분&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;미끄럼 방지장치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH109" s="32" t="inlineStr">
@@ -15388,12 +15396,12 @@
       </c>
       <c r="AH111" s="32" t="inlineStr">
         <is>
-          <t>① Tilt meter 는 인접 건물의 기울기를 잰다.&lt;br&gt;③ Strain gauge 는 부재의 변형률을 잰다.&lt;br&gt;④ Load cell 은 버팀보와 앵커의 축하중을 잰다.</t>
+          <t>① Tilt meter는 인접 건물의 기울기를 잰다.&lt;br&gt;③ Strain gauge는 부재의 변형률을 잰다.&lt;br&gt;④ Load cell은 버팀보와 앵커의 축하중을 잰다.</t>
         </is>
       </c>
       <c r="AI111" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;흙막이 계측기기&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「흙」을 재는가 「부재」를 재는가 「건물」을 재는가&lt;/strong&gt;로 가른다. &lt;strong&gt;Inclinometer 는 흙, Tiltmeter 는 건물&lt;/strong&gt;이다. 둘 다 「기울기」라 헷갈리기 쉽다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;지반 변형은 Inclinometer&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;흙막이 계측기기&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「흙」을 재는가 「부재」를 재는가 「건물」을 재는가&lt;/strong&gt;로 가른다. &lt;strong&gt;Inclinometer는 흙, Tiltmeter는 건물&lt;/strong&gt;이다. 둘 다 「기울기」라 헷갈리기 쉽다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;지반 변형은 Inclinometer&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -15512,7 +15520,7 @@
       </c>
       <c r="AG112" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;침하를 유도한다&lt;/strong&gt;는 것은 목적이 될 수 없다. 지반조사는 &lt;strong&gt;침하를 막기 위해&lt;/strong&gt; 하는 것이다.</t>
+          <t>&lt;strong&gt;침하를 유도한다&lt;/strong&gt;는 것은 목적이 될 수 없다. 지반조사는 &lt;strong&gt;침하를 막기 위해&lt;/strong&gt;하는 것이다.</t>
         </is>
       </c>
       <c r="AH112" s="32" t="inlineStr">
@@ -15646,7 +15654,7 @@
       </c>
       <c r="AH113" s="32" t="inlineStr">
         <is>
-          <t>① 1 : 1 은 옛 보통흙 습지 범위 안의 값이다.&lt;br&gt;③ 1 : 0.5 는 경암의 기준이다.&lt;br&gt;④ 1 : 0.3 은 어느 기준에도 없다.</t>
+          <t>① 1 : 1은 옛 보통흙 습지 범위 안의 값이다.&lt;br&gt;③ 1 : 0.5는 경암의 기준이다.&lt;br&gt;④ 1 : 0.3은 어느 기준에도 없다.</t>
         </is>
       </c>
       <c r="AI113" s="32" t="inlineStr">
@@ -15775,7 +15783,7 @@
       </c>
       <c r="AH114" s="32" t="inlineStr">
         <is>
-          <t>① 3 [m] 는 계단의 기준이다.&lt;br&gt;② 4 [m] 라는 기준은 없다.&lt;br&gt;④ 6 [m] 도 없다.</t>
+          <t>① 3 [m]는 계단의 기준이다.&lt;br&gt;② 4 [m]라는 기준은 없다.&lt;br&gt;④ 6 [m] 도 없다.</t>
         </is>
       </c>
       <c r="AI114" s="32" t="inlineStr">
@@ -16028,7 +16036,7 @@
       </c>
       <c r="AG116" s="32" t="inlineStr">
         <is>
-          <t>교량은 &lt;strong&gt;최대 지간길이 50 [m] 이상&lt;/strong&gt; 이라야 한다. 40 [m] 는 미달이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;건설공사 유해위험방지계획서 제출 대상&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;공사&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기의 값&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;굴착&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;깊이 10 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [m] 면 해당&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;댐&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;저수용량 2천만 [t] 이상인 다목적댐 등&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;해당&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;다리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최대 지간길이 50 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;40 [m] 는 미달&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;냉동·냉장창고시설&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;연면적 5천 [㎡] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5,000 [㎡] 면 해당&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;건축물 · 인공구조물&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;지상높이 31 [m] 이상&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;터널&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;모든 터널&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>교량은 &lt;strong&gt;최대 지간길이 50 [m] 이상&lt;/strong&gt;이라야 한다. 40 [m]는 미달이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;건설공사 유해위험방지계획서 제출 대상&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;공사&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기의 값&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;굴착&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;깊이 10 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [m] 면 해당&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;댐&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;저수용량 2천만 [t] 이상인 다목적댐 등&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;해당&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;다리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최대 지간길이 50 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;40 [m]는 미달&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;냉동·냉장창고시설&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;연면적 5천 [㎡] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5,000 [㎡] 면 해당&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;건축물 · 인공구조물&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;지상높이 31 [m] 이상&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;터널&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;모든 터널&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH116" s="32" t="inlineStr">
@@ -16038,7 +16046,7 @@
       </c>
       <c r="AI116" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;시행령 제42조 — 유해위험방지계획서 제출 대상 건설공사&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;높이 31 · 지간 50 · 깊이 10 · 연면적 3만(냉동냉장창고 등은 5천)&lt;/strong&gt;이 핵심 숫자다. &lt;strong&gt;40 [m] 를 지간길이 기준처럼 보이게 놓는&lt;/strong&gt; 것이 단골 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;지간 50 [m] 이상&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건법 시행령 시행 2026. 8. 1.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EB%B2%95%EC%8B%9C%ED%96%89%EB%A0%B9/%EC%A0%9C42%EC%A1%B0" target="_blank"&gt;제42조(유해위험방지계획서 제출 대상)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건법 시행령 · 시행 2026. 8. 1.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;① 법 제42조제1항제1호에서 "대통령령으로 정하는 사업의 종류 및 규모에 해당하는 사업"이란 다음 각 호의 어느 하나에 해당하는 사업으로서 전기 계약용량이 300킬로와트 이상인 경우를 말한다.&lt;br&gt; 1. 금속가공제품 제조업; 기계 및 가구 제외&lt;br&gt; 2. 비금속 광물제품 제조업&lt;br&gt; 3. 기타 기계 및 장비 제조업&lt;br&gt; 4. 자동차 및 트레일러 제조업&lt;br&gt; 5. 식료품 제조업&lt;br&gt; 6. 고무제품 및 플라스틱제품 제조업&lt;br&gt; 7. 목재 및 나무제품 제조업&lt;br&gt; 8. 기타 제품 제조업&lt;br&gt; 9. 1차 금속 제조업&lt;br&gt; 10. 가구 제조업&lt;br&gt; 11. 화학물질 및 화학제품 제조업&lt;br&gt; 12. 반도체 제조업&lt;br&gt; 13. 전자부품 제조업&lt;br&gt;② 법 제42조제1항제2호에서 "대통령령으로 정하는 기계ㆍ기구 및 설비"란 다음 각 호의 어느 하나에 해당하는 기계ㆍ기구 및 설비를 말한다. 이 경우 다음 각 호에 해당하는 기계ㆍ기구 및 설비의 구체적인 범위는 고용노동부장관이 정하여 고시한다. &amp;lt;개정 2021.11.19&amp;gt;&lt;br&gt; 1. 금속이나 그 밖의 광물의 용해로&lt;br&gt; 2. 화학설비&lt;br&gt; 3. 건조설비&lt;br&gt; 4. 가스집합 용접장치&lt;br&gt; 5. 근로자의 건강에 상당한 장해를 일으킬 우려가 있는 물질로서 고용노동부령으로 정하는 물질의 밀폐ㆍ환기ㆍ배기를 위한 설비&lt;br&gt; 6. 삭제&amp;lt;2021.11.19&amp;gt;&lt;br&gt;③ 법 제42조제1항제3호에서 "대통령령으로 정하는 크기 높이 등에 해당하는 건설공사"란 다음 각 호의 어느 하나에 해당하는 공사를 말한다.&lt;br&gt; 1. 다음 각 목의 어느 하나에 해당하는 건축물 또는 시설 등의 건설ㆍ개조 또는 해체(이하 "건설등"이라 한다) 공사&lt;br&gt; 가. 지상높이가 31미터 이상인 건축물 또는 인공구조물&lt;br&gt; 나. 연면적 3만제곱미터 이상인 건축물&lt;br&gt; 다. 연면적 5천제곱미터 이상인 시설로서 다음의 어느 하나에 해당하는 시설&lt;br&gt; 1) 문화 및 집회시설(전시장 및 동물원ㆍ식물원은 제외한다)&lt;br&gt; 2) 판매시설, 운수시설(고속철도의 역사 및 집배송시설은 제외한다)&lt;br&gt; 3) 종교시설&lt;br&gt; 4) 의료시설 중 종합병원&lt;br&gt; 5) 숙박시설 중 관광숙박시설&lt;br&gt; 6) 지하도상가&lt;br&gt; 7) 냉동ㆍ냉장 창고시설&lt;br&gt; 2. 연면적 5천제곱미터 이상인 냉동ㆍ냉장 창고시설의 설비공사 및 단열공사&lt;br&gt;▶  3. 최대 지간(支間)길이(다리의 기둥과 기둥의 중심사이의 거리)가 50미터 이상인 다리의 건설등 공사&lt;br&gt; 4. 터널의 건설등 공사&lt;br&gt; 5. 다목적댐, 발전용댐, 저수용량 2천만톤 이상의 용수 전용 댐 및 지방상수도 전용 댐의 건설등 공사&lt;br&gt; 6. 깊이 10미터 이상인 굴착공사&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;시행령 제42조 — 유해위험방지계획서 제출 대상 건설공사&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;높이 31 · 지간 50 · 깊이 10 · 연면적 3만(냉동냉장창고 등은 5천)&lt;/strong&gt;이 핵심 숫자다. &lt;strong&gt;40 [m]를 지간길이 기준처럼 보이게 놓는&lt;/strong&gt; 것이 단골 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;지간 50 [m] 이상&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건법 시행령 시행 2026. 8. 1.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EB%B2%95%EC%8B%9C%ED%96%89%EB%A0%B9/%EC%A0%9C42%EC%A1%B0" target="_blank"&gt;제42조(유해위험방지계획서 제출 대상)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건법 시행령 · 시행 2026. 8. 1.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;① 법 제42조제1항제1호에서 "대통령령으로 정하는 사업의 종류 및 규모에 해당하는 사업"이란 다음 각 호의 어느 하나에 해당하는 사업으로서 전기 계약용량이 300킬로와트 이상인 경우를 말한다.&lt;br&gt; 1. 금속가공제품 제조업; 기계 및 가구 제외&lt;br&gt; 2. 비금속 광물제품 제조업&lt;br&gt; 3. 기타 기계 및 장비 제조업&lt;br&gt; 4. 자동차 및 트레일러 제조업&lt;br&gt; 5. 식료품 제조업&lt;br&gt; 6. 고무제품 및 플라스틱제품 제조업&lt;br&gt; 7. 목재 및 나무제품 제조업&lt;br&gt; 8. 기타 제품 제조업&lt;br&gt; 9. 1차 금속 제조업&lt;br&gt; 10. 가구 제조업&lt;br&gt; 11. 화학물질 및 화학제품 제조업&lt;br&gt; 12. 반도체 제조업&lt;br&gt; 13. 전자부품 제조업&lt;br&gt;② 법 제42조제1항제2호에서 "대통령령으로 정하는 기계ㆍ기구 및 설비"란 다음 각 호의 어느 하나에 해당하는 기계ㆍ기구 및 설비를 말한다. 이 경우 다음 각 호에 해당하는 기계ㆍ기구 및 설비의 구체적인 범위는 고용노동부장관이 정하여 고시한다. &amp;lt;개정 2021.11.19&amp;gt;&lt;br&gt; 1. 금속이나 그 밖의 광물의 용해로&lt;br&gt; 2. 화학설비&lt;br&gt; 3. 건조설비&lt;br&gt; 4. 가스집합 용접장치&lt;br&gt; 5. 근로자의 건강에 상당한 장해를 일으킬 우려가 있는 물질로서 고용노동부령으로 정하는 물질의 밀폐ㆍ환기ㆍ배기를 위한 설비&lt;br&gt; 6. 삭제&amp;lt;2021.11.19&amp;gt;&lt;br&gt;③ 법 제42조제1항제3호에서 "대통령령으로 정하는 크기 높이 등에 해당하는 건설공사"란 다음 각 호의 어느 하나에 해당하는 공사를 말한다.&lt;br&gt; 1. 다음 각 목의 어느 하나에 해당하는 건축물 또는 시설 등의 건설ㆍ개조 또는 해체(이하 "건설등"이라 한다) 공사&lt;br&gt; 가. 지상높이가 31미터 이상인 건축물 또는 인공구조물&lt;br&gt; 나. 연면적 3만제곱미터 이상인 건축물&lt;br&gt; 다. 연면적 5천제곱미터 이상인 시설로서 다음의 어느 하나에 해당하는 시설&lt;br&gt; 1) 문화 및 집회시설(전시장 및 동물원ㆍ식물원은 제외한다)&lt;br&gt; 2) 판매시설, 운수시설(고속철도의 역사 및 집배송시설은 제외한다)&lt;br&gt; 3) 종교시설&lt;br&gt; 4) 의료시설 중 종합병원&lt;br&gt; 5) 숙박시설 중 관광숙박시설&lt;br&gt; 6) 지하도상가&lt;br&gt; 7) 냉동ㆍ냉장 창고시설&lt;br&gt; 2. 연면적 5천제곱미터 이상인 냉동ㆍ냉장 창고시설의 설비공사 및 단열공사&lt;br&gt;▶  3. 최대 지간(支間)길이(다리의 기둥과 기둥의 중심사이의 거리)가 50미터 이상인 다리의 건설등 공사&lt;br&gt; 4. 터널의 건설등 공사&lt;br&gt; 5. 다목적댐, 발전용댐, 저수용량 2천만톤 이상의 용수 전용 댐 및 지방상수도 전용 댐의 건설등 공사&lt;br&gt; 6. 깊이 10미터 이상인 굴착공사&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -16296,7 +16304,7 @@
       </c>
       <c r="AI118" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;감전 위험도의 결정 요인&lt;/strong&gt;&lt;br&gt;전압은 &lt;strong&gt;인체저항과 함께 전류를 만드는 재료&lt;/strong&gt; 일 뿐이다. 같은 전압이라도 &lt;strong&gt;젖어 있으면 저항이 1/25 로 떨어져&lt;/strong&gt; 전류가 훨씬 커진다. &lt;strong&gt;실제로 몸에 흐른 전류&lt;/strong&gt;가 위험을 정한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;전압이 아니라 전류&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;감전 위험도의 결정 요인&lt;/strong&gt;&lt;br&gt;전압은 &lt;strong&gt;인체저항과 함께 전류를 만드는 재료&lt;/strong&gt;일 뿐이다. 같은 전압이라도 &lt;strong&gt;젖어 있으면 저항이 1/25로 떨어져&lt;/strong&gt; 전류가 훨씬 커진다. &lt;strong&gt;실제로 몸에 흐른 전류&lt;/strong&gt;가 위험을 정한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;전압이 아니라 전류&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -16419,12 +16427,12 @@
       </c>
       <c r="AG119" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;20 [cm] 이상&lt;/strong&gt;이다. 조립·해체 중에는 정식 작업발판을 놓을 수 없으므로 &lt;strong&gt;폭 기준을 40 [cm] 에서 20 [cm] 로 낮추되 안전대를 함께&lt;/strong&gt; 쓰게 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;발판 폭의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;경우&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;폭&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;일반 작업발판&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;40 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;높이 2 [m] 이상 작업장소&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;달비계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;20 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;매달린 구조&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비계 조립·해체·변경 작업 중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;20 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전대를 함께 쓴다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사다리식 통로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;30 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;20 [cm] 이상&lt;/strong&gt;이다. 조립·해체 중에는 정식 작업발판을 놓을 수 없으므로 &lt;strong&gt;폭 기준을 40 [cm]에서 20 [cm]로 낮추되 안전대를 함께&lt;/strong&gt; 쓰게 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;발판 폭의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;경우&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;폭&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;일반 작업발판&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;40 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;높이 2 [m] 이상 작업장소&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;달비계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;20 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;매달린 구조&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비계 조립·해체·변경 작업 중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;20 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전대를 함께 쓴다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사다리식 통로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;30 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH119" s="32" t="inlineStr">
         <is>
-          <t>① 15 [cm] 는 발판 폭 기준이 아니다.&lt;br&gt;③ 25 [cm] 도 아니다.&lt;br&gt;④ 30 [cm] 는 사다리식 통로의 폭이다.</t>
+          <t>① 15 [cm]는 발판 폭 기준이 아니다.&lt;br&gt;③ 25 [cm] 도 아니다.&lt;br&gt;④ 30 [cm]는 사다리식 통로의 폭이다.</t>
         </is>
       </c>
       <c r="AI119" s="32" t="inlineStr">
@@ -16548,7 +16556,7 @@
       </c>
       <c r="AG120" s="32" t="inlineStr">
         <is>
-          <t>굴착은 &lt;strong&gt;깊이 10 [m] 이상&lt;/strong&gt; 이라야 한다. 9 [m] 는 미달이다.</t>
+          <t>굴착은 &lt;strong&gt;깊이 10 [m] 이상&lt;/strong&gt;이라야 한다. 9 [m]는 미달이다.</t>
         </is>
       </c>
       <c r="AH120" s="32" t="inlineStr">
@@ -16682,12 +16690,12 @@
       </c>
       <c r="AH121" s="32" t="inlineStr">
         <is>
-          <t>① 1.85 [%] 는 다른 공사종류의 값이다.&lt;br&gt;③ 3.09 [%] 도 다른 공사종류의 값이다.&lt;br&gt;④ 3.43 [%] 는 특수·기타 건설공사 쪽 값이다.</t>
+          <t>① 1.85 [%]는 다른 공사종류의 값이다.&lt;br&gt;③ 3.09 [%] 도 다른 공사종류의 값이다.&lt;br&gt;④ 3.43 [%]는 특수·기타 건설공사 쪽 값이다.</t>
         </is>
       </c>
       <c r="AI121" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;산업안전보건관리비 계상 및 사용기준 고시 별표1&lt;/strong&gt;&lt;br&gt;구조는 개정 뒤에도 같다 — &lt;strong&gt;5억 미만과 50억 이상은 비율만, 그 사이 구간만 기초액이 붙는다&lt;/strong&gt;. &lt;strong&gt;대상액은 재료비 + 직접노무비&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;가운데 구간에만 기초액&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; &lt;u&gt;고시 제2024-53호&lt;/u&gt;로 &lt;u&gt;공사종류가 「건축공사 · 토목공사 · 중건설공사 · 특수건설공사」로 개편&lt;/u&gt; 되면서 &lt;u&gt;「철도·궤도신설공사」라는 구분이 사라졌고&lt;/u&gt; 요율도 바뀌었다. 여기 나온 2.45 [%] 는 &lt;u&gt;옛 기준의 값&lt;/u&gt;이다. 다만 &lt;u&gt;공사종류 개편 전에 착공한 공사는 준공 때까지 착공 당시 기준&lt;/u&gt;을 그대로 쓴다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;산업안전보건관리비 계상 및 사용기준 고시 별표1&lt;/strong&gt;&lt;br&gt;구조는 개정 뒤에도 같다 — &lt;strong&gt;5억 미만과 50억 이상은 비율만, 그 사이 구간만 기초액이 붙는다&lt;/strong&gt;. &lt;strong&gt;대상액은 재료비 + 직접노무비&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;가운데 구간에만 기초액&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; &lt;u&gt;고시 제2024-53호&lt;/u&gt;로 &lt;u&gt;공사종류가 「건축공사 · 토목공사 · 중건설공사 · 특수건설공사」로 개편&lt;/u&gt; 되면서 &lt;u&gt;「철도·궤도신설공사」라는 구분이 사라졌고&lt;/u&gt; 요율도 바뀌었다. 여기 나온 2.45 [%]는 &lt;u&gt;옛 기준의 값&lt;/u&gt;이다. 다만 &lt;u&gt;공사종류 개편 전에 착공한 공사는 준공 때까지 착공 당시 기준&lt;/u&gt;을 그대로 쓴다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -16806,12 +16814,12 @@
       </c>
       <c r="AG122" s="32" t="inlineStr">
         <is>
-          <t>권상용 와이어로프의 안전계수는 &lt;strong&gt;5 이상&lt;/strong&gt;이다. 4 가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;항타기·항발기의 와이어로프 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;권상용 와이어로프의 안전계수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4 가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;드럼에 남는 감김 수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2회 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;끊어진 소선의 수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [%] 이상이면 사용 금지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;필러선 제외&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지름의 감소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;공칭지름의 7 [%] 초과면 사용 금지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>권상용 와이어로프의 안전계수는 &lt;strong&gt;5 이상&lt;/strong&gt;이다. 4가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;항타기·항발기의 와이어로프 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;권상용 와이어로프의 안전계수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;드럼에 남는 감김 수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2회 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;끊어진 소선의 수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [%] 이상이면 사용 금지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;필러선 제외&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지름의 감소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;공칭지름의 7 [%] 초과면 사용 금지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH122" s="32" t="inlineStr">
         <is>
-          <t>① 도괴방지를 위해 내력을 확인하고 보강하는 것은 맞다.&lt;br&gt;② 끊어진 소선이 10 [%] 이상이면 쓸 수 없는 것도 맞다.&lt;br&gt;③ 지름 감소가 공칭지름의 7 [%] 를 넘으면 쓸 수 없는 것도 맞다.</t>
+          <t>① 도괴방지를 위해 내력을 확인하고 보강하는 것은 맞다.&lt;br&gt;② 끊어진 소선이 10 [%] 이상이면 쓸 수 없는 것도 맞다.&lt;br&gt;③ 지름 감소가 공칭지름의 7 [%]를 넘으면 쓸 수 없는 것도 맞다.</t>
         </is>
       </c>
       <c r="AI122" s="32" t="inlineStr">
